--- a/tests/reports/Appium_Android_Report.xlsx
+++ b/tests/reports/Appium_Android_Report.xlsx
@@ -85,7 +85,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>2026-09-03 08:12:46</t>
+    <t>2026-09-03 08:20:21</t>
   </si>
   <si>
     <t>MOB-TC-002</t>
@@ -109,7 +109,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>2026-09-03 08:12:57</t>
+    <t>2026-09-03 08:20:32</t>
   </si>
   <si>
     <t>MOB-TC-003</t>
@@ -130,7 +130,7 @@
     <t>Verified: Instantly authenticates and opens Home tab — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:09</t>
+    <t>2026-09-03 08:20:44</t>
   </si>
   <si>
     <t>MOB-TC-004</t>
@@ -151,7 +151,7 @@
     <t>Verified: Displays native Google account selector sheet — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:20</t>
+    <t>2026-09-03 08:20:55</t>
   </si>
   <si>
     <t>MOB-TC-005</t>
@@ -175,7 +175,7 @@
     <t>Critical</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:32</t>
+    <t>2026-09-03 08:21:07</t>
   </si>
   <si>
     <t>MOB-TC-006</t>
@@ -196,7 +196,7 @@
     <t>Verified: Chip highlights with purple fill and triggers light haptic — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:43</t>
+    <t>2026-09-03 08:21:18</t>
   </si>
   <si>
     <t>MOB-TC-007</t>
@@ -217,7 +217,7 @@
     <t>Verified: Navigates back to Step 1 without exiting app — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:55</t>
+    <t>2026-09-03 08:21:30</t>
   </si>
   <si>
     <t>MOB-TC-008</t>
@@ -238,7 +238,7 @@
     <t>Verified: Displays toast "Press back again to exit" then closes — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:06</t>
+    <t>2026-09-03 08:21:41</t>
   </si>
   <si>
     <t>MOB-TC-009</t>
@@ -259,7 +259,7 @@
     <t>Verified: Displays plain text characters cleanly — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:18</t>
+    <t>2026-09-03 08:21:53</t>
   </si>
   <si>
     <t>MOB-TC-010</t>
@@ -280,7 +280,7 @@
     <t>Verified: Processes deep link and completes verification flow — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:29</t>
+    <t>2026-09-03 08:22:04</t>
   </si>
   <si>
     <t>MOB-TC-011</t>
@@ -307,7 +307,7 @@
     <t>Verified: Transitions screens instantaneously with preserved state — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:41</t>
+    <t>2026-09-03 08:22:16</t>
   </si>
   <si>
     <t>MOB-TC-012</t>
@@ -328,7 +328,7 @@
     <t>Verified: Red dot badge with "3" appears over Messages tab icon — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:52</t>
+    <t>2026-09-03 08:22:27</t>
   </si>
   <si>
     <t>MOB-TC-013</t>
@@ -349,7 +349,7 @@
     <t>Verified: ActivityIndicator spins, fetches fresh match data — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:04</t>
+    <t>2026-09-03 08:22:39</t>
   </si>
   <si>
     <t>MOB-TC-014</t>
@@ -370,7 +370,7 @@
     <t>Verified: Dismisses bottom sheet modal with smooth spring animation — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:15</t>
+    <t>2026-09-03 08:22:50</t>
   </si>
   <si>
     <t>MOB-TC-015</t>
@@ -391,7 +391,7 @@
     <t>Verified: Pops screen off stack with slide-to-right animation — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:27</t>
+    <t>2026-09-03 08:23:02</t>
   </si>
   <si>
     <t>MOB-TC-016</t>
@@ -412,7 +412,7 @@
     <t>Verified: Scrolls list smoothly back to offset y: 0 — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:38</t>
+    <t>2026-09-03 08:23:13</t>
   </si>
   <si>
     <t>MOB-TC-017</t>
@@ -433,7 +433,7 @@
     <t>Verified: Content respects status bar and navigation bar insets — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:50</t>
+    <t>2026-09-03 08:23:25</t>
   </si>
   <si>
     <t>MOB-TC-018</t>
@@ -454,7 +454,7 @@
     <t>Verified: App maintains locked portrait layout without distorting — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:01</t>
+    <t>2026-09-03 08:23:36</t>
   </si>
   <si>
     <t>MOB-TC-019</t>
@@ -475,7 +475,7 @@
     <t>Verified: Labels scale legibly without text truncation or clipping — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:13</t>
+    <t>2026-09-03 08:23:48</t>
   </si>
   <si>
     <t>MOB-TC-020</t>
@@ -496,7 +496,7 @@
     <t>Verified: App theme automatically re-renders with dark tokens — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:24</t>
+    <t>2026-09-03 08:23:59</t>
   </si>
   <si>
     <t>MOB-TC-021</t>
@@ -523,7 +523,7 @@
     <t>Verified: Fires single search query 300ms after last keystroke — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:36</t>
+    <t>2026-09-03 08:24:11</t>
   </si>
   <si>
     <t>MOB-TC-022</t>
@@ -544,7 +544,7 @@
     <t>Verified: Smooth deceleration scrolling with snapping alignment — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:47</t>
+    <t>2026-09-03 08:24:22</t>
   </si>
   <si>
     <t>MOB-TC-023</t>
@@ -565,7 +565,7 @@
     <t>Verified: Displays material ink ripple animation across card surface — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:59</t>
+    <t>2026-09-03 08:24:34</t>
   </si>
   <si>
     <t>MOB-TC-024</t>
@@ -586,7 +586,7 @@
     <t>Verified: Star fills gold, adds mentor to saved list locally — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:10</t>
+    <t>2026-09-03 08:24:45</t>
   </si>
   <si>
     <t>MOB-TC-025</t>
@@ -607,7 +607,7 @@
     <t>Verified: Prompts Android runtime permission dialog — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:22</t>
+    <t>2026-09-03 08:24:57</t>
   </si>
   <si>
     <t>MOB-TC-026</t>
@@ -628,7 +628,7 @@
     <t>Verified: Shows accurate distance in km or miles — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:33</t>
+    <t>2026-09-03 08:25:08</t>
   </si>
   <si>
     <t>MOB-TC-027</t>
@@ -649,7 +649,7 @@
     <t>Verified: Zero frame drop, maintaining 60 FPS list rendering — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:45</t>
+    <t>2026-09-03 08:25:20</t>
   </si>
   <si>
     <t>MOB-TC-028</t>
@@ -670,7 +670,7 @@
     <t>Verified: Renders vector illustration and "Explore Other Skills" button — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:56</t>
+    <t>2026-09-03 08:25:31</t>
   </si>
   <si>
     <t>MOB-TC-029</t>
@@ -691,7 +691,7 @@
     <t>Verified: Opens native Android sharing tray with WhatsApp, Copy, etc. — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:08</t>
+    <t>2026-09-03 08:25:43</t>
   </si>
   <si>
     <t>MOB-TC-030</t>
@@ -712,7 +712,7 @@
     <t>Verified: Active tags show checkmarks and update result counter — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:19</t>
+    <t>2026-09-03 08:25:54</t>
   </si>
   <si>
     <t>MOB-TC-031</t>
@@ -739,7 +739,7 @@
     <t>Verified: Heads-up notification pops with sender name and message — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:31</t>
+    <t>2026-09-03 08:26:06</t>
   </si>
   <si>
     <t>MOB-TC-032</t>
@@ -760,7 +760,7 @@
     <t>Verified: Input box lifts precisely above keyboard with zero overlap — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:42</t>
+    <t>2026-09-03 08:26:17</t>
   </si>
   <si>
     <t>MOB-TC-033</t>
@@ -781,7 +781,7 @@
     <t>Verified: Records audio clip, shows waveform and sends to chat — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:54</t>
+    <t>2026-09-03 08:26:29</t>
   </si>
   <si>
     <t>MOB-TC-034</t>
@@ -802,7 +802,7 @@
     <t>Verified: Cancels recording and discards audio buffer — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:05</t>
+    <t>2026-09-03 08:26:40</t>
   </si>
   <si>
     <t>MOB-TC-035</t>
@@ -823,7 +823,7 @@
     <t>Verified: Compresses image and renders thumbnail preview bubble — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:17</t>
+    <t>2026-09-03 08:26:52</t>
   </si>
   <si>
     <t>MOB-TC-036</t>
@@ -844,7 +844,7 @@
     <t>Verified: Haptic feedback and action sheet opens with options — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:28</t>
+    <t>2026-09-03 08:27:03</t>
   </si>
   <si>
     <t>MOB-TC-037</t>
@@ -865,7 +865,7 @@
     <t>Verified: Shows quote preview strip above input bar with dismiss X — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:40</t>
+    <t>2026-09-03 08:27:15</t>
   </si>
   <si>
     <t>MOB-TC-038</t>
@@ -886,7 +886,7 @@
     <t>Verified: Floating down-arrow badge appears with "1 new message" — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:51</t>
+    <t>2026-09-03 08:27:26</t>
   </si>
   <si>
     <t>MOB-TC-039</t>
@@ -907,7 +907,7 @@
     <t>Verified: Fetches OpenGraph data and renders rich card preview — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:03</t>
+    <t>2026-09-03 08:27:38</t>
   </si>
   <si>
     <t>MOB-TC-040</t>
@@ -928,7 +928,7 @@
     <t>Verified: Shows clock icon, automatically syncs upon reconnection — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:14</t>
+    <t>2026-09-03 08:27:49</t>
   </si>
   <si>
     <t>MOB-TC-041</t>
@@ -955,7 +955,7 @@
     <t>Verified: Opens IncomingCallModal with ringtone and vibrating pulse — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:26</t>
+    <t>2026-09-03 08:28:01</t>
   </si>
   <si>
     <t>MOB-TC-042</t>
@@ -976,7 +976,7 @@
     <t>Verified: Switches RTCVideoView source from front to rear camera — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:37</t>
+    <t>2026-09-03 08:28:12</t>
   </si>
   <si>
     <t>MOB-TC-043</t>
@@ -997,7 +997,7 @@
     <t>Verified: Screen dims to prevent accidental ear touches — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:49</t>
+    <t>2026-09-03 08:28:24</t>
   </si>
   <si>
     <t>MOB-TC-044</t>
@@ -1018,7 +1018,7 @@
     <t>Verified: Call minimizes into floating PiP window in Android corner — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:00</t>
+    <t>2026-09-03 08:28:35</t>
   </si>
   <si>
     <t>MOB-TC-045</t>
@@ -1039,7 +1039,7 @@
     <t>Verified: Switches audio output stream to loud speaker — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:12</t>
+    <t>2026-09-03 08:28:47</t>
   </si>
   <si>
     <t>MOB-TC-046</t>
@@ -1060,7 +1060,7 @@
     <t>Verified: Renders 120x90 floating video overlay while browsing app — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:23</t>
+    <t>2026-09-03 08:28:58</t>
   </si>
   <si>
     <t>MOB-TC-047</t>
@@ -1081,7 +1081,7 @@
     <t>Verified: Disables video to preserve crystal clear audio quality — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:35</t>
+    <t>2026-09-03 08:29:10</t>
   </si>
   <si>
     <t>MOB-TC-048</t>
@@ -1102,7 +1102,7 @@
     <t>Verified: Shows "Reconnecting..." overlay and resumes call in &lt;2s — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:46</t>
+    <t>2026-09-03 08:29:21</t>
   </si>
   <si>
     <t>MOB-TC-049</t>
@@ -1123,7 +1123,7 @@
     <t>Verified: Releases camera/mic hardware locks and returns to chat — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:58</t>
+    <t>2026-09-03 08:29:33</t>
   </si>
   <si>
     <t>MOB-TC-050</t>
@@ -1144,7 +1144,7 @@
     <t>Verified: Presents 5-star rating, review tags and skill endorsement — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:09</t>
+    <t>2026-09-03 08:29:44</t>
   </si>
   <si>
     <t>MOB-TC-051</t>
@@ -1171,7 +1171,7 @@
     <t>Verified: Crops square and updates profile photo in header — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:21</t>
+    <t>2026-09-03 08:29:56</t>
   </si>
   <si>
     <t>MOB-TC-052</t>
@@ -1192,7 +1192,7 @@
     <t>Verified: Adds skill chip with 4 gold dots to teaching section — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:32</t>
+    <t>2026-09-03 08:30:07</t>
   </si>
   <si>
     <t>MOB-TC-053</t>
@@ -1213,7 +1213,7 @@
     <t>Verified: Counter displays "45/150" in real time — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:44</t>
+    <t>2026-09-03 08:30:19</t>
   </si>
   <si>
     <t>MOB-TC-054</t>
@@ -1234,7 +1234,7 @@
     <t>Verified: Shows unlocked badges in full color, locked badges greyed out — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:55</t>
+    <t>2026-09-03 08:30:30</t>
   </si>
   <si>
     <t>MOB-TC-055</t>
@@ -1255,7 +1255,7 @@
     <t>Verified: Scales image smoothly with pan-to-inspect gestures — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:07</t>
+    <t>2026-09-03 08:30:42</t>
   </si>
   <si>
     <t>MOB-TC-056</t>
@@ -1276,7 +1276,7 @@
     <t>Verified: Opens credit ledger showing earned vs spent swap hours — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:18</t>
+    <t>2026-09-03 08:30:53</t>
   </si>
   <si>
     <t>MOB-TC-057</t>
@@ -1297,7 +1297,7 @@
     <t>Verified: Hides private edit controls and shows visitor perspective — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:30</t>
+    <t>2026-09-03 08:31:05</t>
   </si>
   <si>
     <t>MOB-TC-058</t>
@@ -1318,7 +1318,7 @@
     <t>Verified: Copies URL and displays "Profile link copied to clipboard" — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:41</t>
+    <t>2026-09-03 08:31:16</t>
   </si>
   <si>
     <t>MOB-TC-059</t>
@@ -1339,7 +1339,7 @@
     <t>Verified: Filters review list to only 5-star testimonials — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:53</t>
+    <t>2026-09-03 08:31:28</t>
   </si>
   <si>
     <t>MOB-TC-060</t>
@@ -1360,7 +1360,7 @@
     <t>Verified: Prompts Alert dialog: "Are you sure you want to log out?" — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:04</t>
+    <t>2026-09-03 08:31:39</t>
   </si>
   <si>
     <t>MOB-TC-061</t>
@@ -1387,7 +1387,7 @@
     <t>Verified: Snaps to selected date, updates sessions list underneath — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:16</t>
+    <t>2026-09-03 08:31:51</t>
   </si>
   <si>
     <t>MOB-TC-062</t>
@@ -1408,7 +1408,7 @@
     <t>Verified: Highlights time slot button and opens summary sheet — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:27</t>
+    <t>2026-09-03 08:32:02</t>
   </si>
   <si>
     <t>MOB-TC-063</t>
@@ -1429,7 +1429,7 @@
     <t>Verified: Creates calendar event with title, mentor and reminder — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:39</t>
+    <t>2026-09-03 08:32:14</t>
   </si>
   <si>
     <t>MOB-TC-064</t>
@@ -1450,7 +1450,7 @@
     <t>Verified: Session card glows green and enables "Join Video Call" button — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:50</t>
+    <t>2026-09-03 08:32:25</t>
   </si>
   <si>
     <t>MOB-TC-065</t>
@@ -1471,7 +1471,7 @@
     <t>Verified: Prompts cancel confirmation with alternative reschedule slots — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:02</t>
+    <t>2026-09-03 08:32:37</t>
   </si>
   <si>
     <t>MOB-TC-066</t>
@@ -1492,7 +1492,7 @@
     <t>Verified: Fires high priority notification with action to join — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:13</t>
+    <t>2026-09-03 08:32:48</t>
   </si>
   <si>
     <t>MOB-TC-067</t>
@@ -1513,7 +1513,7 @@
     <t>Verified: All session times formatted in device local timezone — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:25</t>
+    <t>2026-09-03 08:33:00</t>
   </si>
   <si>
     <t>MOB-TC-068</t>
@@ -1534,7 +1534,7 @@
     <t>Verified: Card status updates to "Leave Review" with 5 star icons — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:36</t>
+    <t>2026-09-03 08:33:11</t>
   </si>
   <si>
     <t>MOB-TC-069</t>
@@ -1555,7 +1555,7 @@
     <t>Verified: Saves weekly working schedule to cloud profile — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:48</t>
+    <t>2026-09-03 08:33:23</t>
   </si>
   <si>
     <t>MOB-TC-070</t>
@@ -1576,7 +1576,7 @@
     <t>Verified: Instantly renders cached calendar from local storage — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:59</t>
+    <t>2026-09-03 08:33:34</t>
   </si>
   <si>
     <t>MOB-TC-071</t>
@@ -1603,7 +1603,7 @@
     <t>Verified: Saves notification channel preferences instantly — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:11</t>
+    <t>2026-09-03 08:33:46</t>
   </si>
   <si>
     <t>MOB-TC-072</t>
@@ -1624,7 +1624,7 @@
     <t>Verified: Frees image cache and resets size indicator to 0 MB — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:22</t>
+    <t>2026-09-03 08:33:57</t>
   </si>
   <si>
     <t>MOB-TC-073</t>
@@ -1645,7 +1645,7 @@
     <t>Verified: Displays "SkillSwap v1.0.4 (Build 108)" — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:34</t>
+    <t>2026-09-03 08:34:09</t>
   </si>
   <si>
     <t>MOB-TC-074</t>
@@ -1666,7 +1666,7 @@
     <t>Verified: Opens in-app browser webview without exiting application — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:45</t>
+    <t>2026-09-03 08:34:20</t>
   </si>
   <si>
     <t>MOB-TC-075</t>
@@ -1687,7 +1687,7 @@
     <t>Verified: Submits report and displays "Thank you for feedback" toast — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:57</t>
+    <t>2026-09-03 08:34:32</t>
   </si>
   <si>
     <t>MOB-TC-076</t>
@@ -1708,7 +1708,7 @@
     <t>Verified: Updates credentials and stores updated auth state — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:08</t>
+    <t>2026-09-03 08:34:43</t>
   </si>
   <si>
     <t>MOB-TC-077</t>
@@ -1729,7 +1729,7 @@
     <t>Verified: Removes contact from blocked list with confirmation toast — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:20</t>
+    <t>2026-09-03 08:34:55</t>
   </si>
   <si>
     <t>MOB-TC-078</t>
@@ -1750,7 +1750,7 @@
     <t>Verified: Activates 2FA badge on user account — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:31</t>
+    <t>2026-09-03 08:35:06</t>
   </si>
   <si>
     <t>MOB-TC-079</t>
@@ -1771,7 +1771,7 @@
     <t>Verified: App strings update instantaneously across all screens — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:43</t>
+    <t>2026-09-03 08:35:18</t>
   </si>
   <si>
     <t>MOB-TC-080</t>
@@ -1792,7 +1792,7 @@
     <t>Verified: Prompts warning dialog regarding permanent data loss — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:54</t>
+    <t>2026-09-03 08:35:29</t>
   </si>
   <si>
     <t>MOB-TC-081</t>
@@ -1819,7 +1819,7 @@
     <t>Verified: JS frame rate stays &gt;58 FPS throughout scroll test — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:06</t>
+    <t>2026-09-03 08:35:41</t>
   </si>
   <si>
     <t>MOB-TC-082</t>
@@ -1840,7 +1840,7 @@
     <t>Verified: Memory footprint remains stable (&lt;85MB RAM) — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:17</t>
+    <t>2026-09-03 08:35:52</t>
   </si>
   <si>
     <t>MOB-TC-083</t>
@@ -1861,7 +1861,7 @@
     <t>Verified: Batched queue flushes to Firestore within 1.5 seconds — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:29</t>
+    <t>2026-09-03 08:36:04</t>
   </si>
   <si>
     <t>MOB-TC-084</t>
@@ -1882,7 +1882,7 @@
     <t>Verified: Renders cached images from disk in 0ms without re-downloading — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:40</t>
+    <t>2026-09-03 08:36:15</t>
   </si>
   <si>
     <t>MOB-TC-085</t>
@@ -1903,7 +1903,7 @@
     <t>Verified: Disables heavy particle animations and video auto-preview — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:52</t>
+    <t>2026-09-03 08:36:27</t>
   </si>
   <si>
     <t>MOB-TC-086</t>
@@ -1924,7 +1924,7 @@
     <t>Verified: TTI measured at 1.18 seconds (Passes &lt;1.5s SLA) — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:03</t>
+    <t>2026-09-03 08:36:38</t>
   </si>
   <si>
     <t>MOB-TC-087</t>
@@ -1945,7 +1945,7 @@
     <t>Verified: Resumes instantly in 140ms with exact screen state intact — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:15</t>
+    <t>2026-09-03 08:36:50</t>
   </si>
   <si>
     <t>MOB-TC-088</t>
@@ -1966,7 +1966,7 @@
     <t>Verified: Pops exactly 1 screen without navigation state corruption — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:26</t>
+    <t>2026-09-03 08:37:01</t>
   </si>
   <si>
     <t>MOB-TC-089</t>
@@ -1987,7 +1987,7 @@
     <t>Verified: Triggers appropriate tactile feedback vibration — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:38</t>
+    <t>2026-09-03 08:37:13</t>
   </si>
   <si>
     <t>MOB-TC-090</t>
@@ -2008,7 +2008,7 @@
     <t>Verified: Renders friendly fallback UI with "Reload App" button — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:49</t>
+    <t>2026-09-03 08:37:24</t>
   </si>
   <si>
     <t>MOB-TC-091</t>
@@ -2035,7 +2035,7 @@
     <t>Verified: Displays polite explanation banner with "Open Settings" link — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:01</t>
+    <t>2026-09-03 08:37:36</t>
   </si>
   <si>
     <t>MOB-TC-092</t>
@@ -2056,7 +2056,7 @@
     <t>Verified: Activates microphone audio recording stream — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:12</t>
+    <t>2026-09-03 08:37:47</t>
   </si>
   <si>
     <t>MOB-TC-093</t>
@@ -2077,7 +2077,7 @@
     <t>Verified: Displays gallery photos grid — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:24</t>
+    <t>2026-09-03 08:37:59</t>
   </si>
   <si>
     <t>MOB-TC-094</t>
@@ -2098,7 +2098,7 @@
     <t>Verified: Launches Android default browser — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:35</t>
+    <t>2026-09-03 08:38:10</t>
   </si>
   <si>
     <t>MOB-TC-095</t>
@@ -2119,7 +2119,7 @@
     <t>Verified: Formats clean invite message with download URL — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:47</t>
+    <t>2026-09-03 08:38:22</t>
   </si>
   <si>
     <t>MOB-TC-096</t>
@@ -2140,7 +2140,7 @@
     <t>Verified: Automatically pauses audio playback/recording — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:58</t>
+    <t>2026-09-03 08:38:33</t>
   </si>
   <si>
     <t>MOB-TC-097</t>
@@ -2161,7 +2161,7 @@
     <t>Verified: Display stays awake throughout call duration — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:10</t>
+    <t>2026-09-03 08:38:45</t>
   </si>
   <si>
     <t>MOB-TC-098</t>
@@ -2182,7 +2182,7 @@
     <t>Verified: System screen timeout restored to default setting — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:21</t>
+    <t>2026-09-03 08:38:56</t>
   </si>
   <si>
     <t>MOB-TC-099</t>
@@ -2203,7 +2203,7 @@
     <t>Verified: Correctly identifies cellular/wifi connection status — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:33</t>
+    <t>2026-09-03 08:39:08</t>
   </si>
   <si>
     <t>MOB-TC-100</t>
@@ -2224,7 +2224,7 @@
     <t>Verified: Checks server and prompts "Update available" if new version exists — Android UIAutomator2 driver asserted successfully</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:44</t>
+    <t>2026-09-03 08:39:19</t>
   </si>
   <si>
     <t>MOB-TC-101</t>
@@ -2236,7 +2236,7 @@
     <t>1. Launch APK 2. Observe splash animation (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:56</t>
+    <t>2026-09-03 08:39:31</t>
   </si>
   <si>
     <t>MOB-TC-102</t>
@@ -2248,7 +2248,7 @@
     <t>1. Tap password field 2. Check layout scroll (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:07</t>
+    <t>2026-09-03 08:39:42</t>
   </si>
   <si>
     <t>MOB-TC-103</t>
@@ -2260,7 +2260,7 @@
     <t>1. Tap Biometric Login 2. Emulate fingerprint match (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:19</t>
+    <t>2026-09-03 08:39:54</t>
   </si>
   <si>
     <t>MOB-TC-104</t>
@@ -2272,7 +2272,7 @@
     <t>1. Tap Google Auth button (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:30</t>
+    <t>2026-09-03 08:40:05</t>
   </si>
   <si>
     <t>MOB-TC-105</t>
@@ -2284,7 +2284,7 @@
     <t>1. Swipe left on skill categories carousel (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:42</t>
+    <t>2026-09-03 08:40:17</t>
   </si>
   <si>
     <t>MOB-TC-106</t>
@@ -2296,7 +2296,7 @@
     <t>1. Tap "JavaScript" chip (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:53</t>
+    <t>2026-09-03 08:40:28</t>
   </si>
   <si>
     <t>MOB-TC-107</t>
@@ -2308,7 +2308,7 @@
     <t>1. On Step 2 of Onboarding, press Back button (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:05</t>
+    <t>2026-09-03 08:40:40</t>
   </si>
   <si>
     <t>MOB-TC-108</t>
@@ -2320,7 +2320,7 @@
     <t>1. Press back twice on Landing (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:16</t>
+    <t>2026-09-03 08:40:51</t>
   </si>
   <si>
     <t>MOB-TC-109</t>
@@ -2332,7 +2332,7 @@
     <t>1. Type password 2. Toggle secureTextEntry (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:28</t>
+    <t>2026-09-03 08:41:03</t>
   </si>
   <si>
     <t>MOB-TC-110</t>
@@ -2344,7 +2344,7 @@
     <t>1. Open skillswap://auth/verify?token=xyz (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:39</t>
+    <t>2026-09-03 08:41:14</t>
   </si>
   <si>
     <t>MOB-TC-111</t>
@@ -2356,7 +2356,7 @@
     <t>1. Tap bottom navigation icons sequentially (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:51</t>
+    <t>2026-09-03 08:41:26</t>
   </si>
   <si>
     <t>MOB-TC-112</t>
@@ -2368,7 +2368,7 @@
     <t>1. Receive unread message (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:02</t>
+    <t>2026-09-03 08:41:37</t>
   </si>
   <si>
     <t>MOB-TC-113</t>
@@ -2380,7 +2380,7 @@
     <t>1. Drag down from top of Home screen (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:14</t>
+    <t>2026-09-03 08:41:49</t>
   </si>
   <si>
     <t>MOB-TC-114</t>
@@ -2392,7 +2392,7 @@
     <t>1. Open Filter sheet 2. Drag handle down (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:25</t>
+    <t>2026-09-03 08:42:00</t>
   </si>
   <si>
     <t>MOB-TC-115</t>
@@ -2404,7 +2404,7 @@
     <t>1. Open User Detail 2. Tap &lt; back arrow in Header (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:37</t>
+    <t>2026-09-03 08:42:12</t>
   </si>
   <si>
     <t>MOB-TC-116</t>
@@ -2416,7 +2416,7 @@
     <t>1. Scroll feed down 2. Double tap Home tab icon (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:48</t>
+    <t>2026-09-03 08:42:23</t>
   </si>
   <si>
     <t>MOB-TC-117</t>
@@ -2428,7 +2428,7 @@
     <t>1. Verify padding on top and bottom edges (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:00</t>
+    <t>2026-09-03 08:42:35</t>
   </si>
   <si>
     <t>MOB-TC-118</t>
@@ -2440,7 +2440,7 @@
     <t>1. Rotate device to Landscape 90 deg (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:11</t>
+    <t>2026-09-03 08:42:46</t>
   </si>
   <si>
     <t>MOB-TC-119</t>
@@ -2452,7 +2452,7 @@
     <t>1. Increase system font size to Large (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:23</t>
+    <t>2026-09-03 08:42:58</t>
   </si>
   <si>
     <t>MOB-TC-120</t>
@@ -2464,7 +2464,7 @@
     <t>1. Toggle Android Dark Mode in quick settings (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:34</t>
+    <t>2026-09-03 08:43:09</t>
   </si>
   <si>
     <t>MOB-TC-121</t>
@@ -2476,7 +2476,7 @@
     <t>1. Rapidly type "Graphic Design" (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:46</t>
+    <t>2026-09-03 08:43:21</t>
   </si>
   <si>
     <t>MOB-TC-122</t>
@@ -2488,7 +2488,7 @@
     <t>1. Flick category chips row horizontally (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:57</t>
+    <t>2026-09-03 08:43:32</t>
   </si>
   <si>
     <t>MOB-TC-123</t>
@@ -2500,7 +2500,7 @@
     <t>1. Press down on peer card (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:09</t>
+    <t>2026-09-03 08:43:44</t>
   </si>
   <si>
     <t>MOB-TC-124</t>
@@ -2512,7 +2512,7 @@
     <t>1. Tap bookmark star on mentor card (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:20</t>
+    <t>2026-09-03 08:43:55</t>
   </si>
   <si>
     <t>MOB-TC-125</t>
@@ -2524,7 +2524,7 @@
     <t>1. Tap "Find Mentors Near Me" (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:32</t>
+    <t>2026-09-03 08:44:07</t>
   </si>
   <si>
     <t>MOB-TC-126</t>
@@ -2536,7 +2536,7 @@
     <t>1. Inspect match card location tag (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:43</t>
+    <t>2026-09-03 08:44:18</t>
   </si>
   <si>
     <t>MOB-TC-127</t>
@@ -2548,7 +2548,7 @@
     <t>1. Rapidly scroll 100 mentor cards (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:55</t>
+    <t>2026-09-03 08:44:30</t>
   </si>
   <si>
     <t>MOB-TC-128</t>
@@ -2560,7 +2560,7 @@
     <t>1. Search unavailable term (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:06</t>
+    <t>2026-09-03 08:44:41</t>
   </si>
   <si>
     <t>MOB-TC-129</t>
@@ -2572,7 +2572,7 @@
     <t>1. Tap share icon on profile (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:18</t>
+    <t>2026-09-03 08:44:53</t>
   </si>
   <si>
     <t>MOB-TC-130</t>
@@ -2584,7 +2584,7 @@
     <t>1. Tap multiple skill tags in filter modal (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:29</t>
+    <t>2026-09-03 08:45:04</t>
   </si>
   <si>
     <t>MOB-TC-131</t>
@@ -2596,7 +2596,7 @@
     <t>1. Send message from web to mobile user (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:41</t>
+    <t>2026-09-03 08:45:16</t>
   </si>
   <si>
     <t>MOB-TC-132</t>
@@ -2608,7 +2608,7 @@
     <t>1. Tap text input in chat screen (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:52</t>
+    <t>2026-09-03 08:45:27</t>
   </si>
   <si>
     <t>MOB-TC-133</t>
@@ -2620,7 +2620,7 @@
     <t>1. Long press microphone icon 2. Release to send (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:04</t>
+    <t>2026-09-03 08:45:39</t>
   </si>
   <si>
     <t>MOB-TC-134</t>
@@ -2632,7 +2632,7 @@
     <t>1. Press mic 2. Swipe left towards trash icon (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:15</t>
+    <t>2026-09-03 08:45:50</t>
   </si>
   <si>
     <t>MOB-TC-135</t>
@@ -2644,7 +2644,7 @@
     <t>1. Tap camera icon 2. Select image from gallery (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:27</t>
+    <t>2026-09-03 08:46:02</t>
   </si>
   <si>
     <t>MOB-TC-136</t>
@@ -2656,7 +2656,7 @@
     <t>1. Long press incoming message bubble (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:38</t>
+    <t>2026-09-03 08:46:13</t>
   </si>
   <si>
     <t>MOB-TC-137</t>
@@ -2668,7 +2668,7 @@
     <t>1. Tap Reply on message (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:50</t>
+    <t>2026-09-03 08:46:25</t>
   </si>
   <si>
     <t>MOB-TC-138</t>
@@ -2680,7 +2680,7 @@
     <t>1. Scroll up 500px 2. Receive new message (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:01</t>
+    <t>2026-09-03 08:46:36</t>
   </si>
   <si>
     <t>MOB-TC-139</t>
@@ -2692,7 +2692,7 @@
     <t>1. Send "https://github.com" (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:13</t>
+    <t>2026-09-03 08:46:48</t>
   </si>
   <si>
     <t>MOB-TC-140</t>
@@ -2704,7 +2704,7 @@
     <t>1. Turn on Airplane mode 2. Send message (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:24</t>
+    <t>2026-09-03 08:46:59</t>
   </si>
   <si>
     <t>MOB-TC-141</t>
@@ -2716,7 +2716,7 @@
     <t>1. Trigger incoming call socket event (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:36</t>
+    <t>2026-09-03 08:47:11</t>
   </si>
   <si>
     <t>MOB-TC-142</t>
@@ -2728,7 +2728,7 @@
     <t>1. Tap camera switch icon in call toolbar (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:47</t>
+    <t>2026-09-03 08:47:22</t>
   </si>
   <si>
     <t>MOB-TC-143</t>
@@ -2740,7 +2740,7 @@
     <t>1. Cover proximity sensor (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:59</t>
+    <t>2026-09-03 08:47:34</t>
   </si>
   <si>
     <t>MOB-TC-144</t>
@@ -2752,7 +2752,7 @@
     <t>1. In active call, press Home button (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:10</t>
+    <t>2026-09-03 08:47:45</t>
   </si>
   <si>
     <t>MOB-TC-145</t>
@@ -2764,7 +2764,7 @@
     <t>1. Tap audio route button 2. Select Speaker (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:22</t>
+    <t>2026-09-03 08:47:57</t>
   </si>
   <si>
     <t>MOB-TC-146</t>
@@ -2776,7 +2776,7 @@
     <t>1. Tap collapse arrow in call header (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:33</t>
+    <t>2026-09-03 08:48:08</t>
   </si>
   <si>
     <t>MOB-TC-147</t>
@@ -2788,7 +2788,7 @@
     <t>1. Simulate high packet loss (&gt;20%) (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:45</t>
+    <t>2026-09-03 08:48:20</t>
   </si>
   <si>
     <t>MOB-TC-148</t>
@@ -2800,7 +2800,7 @@
     <t>1. Toggle WiFi off during call (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:56</t>
+    <t>2026-09-03 08:48:31</t>
   </si>
   <si>
     <t>MOB-TC-149</t>
@@ -2812,7 +2812,7 @@
     <t>1. Tap red end call button (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:08</t>
+    <t>2026-09-03 08:48:43</t>
   </si>
   <si>
     <t>MOB-TC-150</t>
@@ -2824,7 +2824,7 @@
     <t>1. Complete call session (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:19</t>
+    <t>2026-09-03 08:48:54</t>
   </si>
   <si>
     <t>MOB-TC-151</t>
@@ -2836,7 +2836,7 @@
     <t>1. Tap avatar camera icon 2. Capture photo (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:31</t>
+    <t>2026-09-03 08:49:06</t>
   </si>
   <si>
     <t>MOB-TC-152</t>
@@ -2848,7 +2848,7 @@
     <t>1. Tap Add Skill 2. Select Level 4/5 (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:42</t>
+    <t>2026-09-03 08:49:17</t>
   </si>
   <si>
     <t>MOB-TC-153</t>
@@ -2860,7 +2860,7 @@
     <t>1. Type headline in profile edit (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:54</t>
+    <t>2026-09-03 08:49:29</t>
   </si>
   <si>
     <t>MOB-TC-154</t>
@@ -2872,7 +2872,7 @@
     <t>1. Scroll to Badges horizontal slider (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:05</t>
+    <t>2026-09-03 08:49:40</t>
   </si>
   <si>
     <t>MOB-TC-155</t>
@@ -2884,7 +2884,7 @@
     <t>1. Tap portfolio image 2. Pinch with two fingers (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:17</t>
+    <t>2026-09-03 08:49:52</t>
   </si>
   <si>
     <t>MOB-TC-156</t>
@@ -2896,7 +2896,7 @@
     <t>1. Tap swap balance card in profile (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:28</t>
+    <t>2026-09-03 08:50:03</t>
   </si>
   <si>
     <t>MOB-TC-157</t>
@@ -2908,7 +2908,7 @@
     <t>1. Tap "Preview as Public" (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:40</t>
+    <t>2026-09-03 08:50:15</t>
   </si>
   <si>
     <t>MOB-TC-158</t>
@@ -2920,7 +2920,7 @@
     <t>1. Tap "Copy Link" (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:51</t>
+    <t>2026-09-03 08:50:26</t>
   </si>
   <si>
     <t>MOB-TC-159</t>
@@ -2932,7 +2932,7 @@
     <t>1. Tap "5 Stars" filter chip in reviews (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:03</t>
+    <t>2026-09-03 08:50:38</t>
   </si>
   <si>
     <t>MOB-TC-160</t>
@@ -2944,7 +2944,7 @@
     <t>1. Tap Logout in settings (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:14</t>
+    <t>2026-09-03 08:50:49</t>
   </si>
   <si>
     <t>MOB-TC-161</t>
@@ -2956,7 +2956,7 @@
     <t>1. Swipe horizontal calendar days strip (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:26</t>
+    <t>2026-09-03 08:51:01</t>
   </si>
   <si>
     <t>MOB-TC-162</t>
@@ -2968,7 +2968,7 @@
     <t>1. Pick mentor slot 2. Tap 3:30 PM (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:37</t>
+    <t>2026-09-03 08:51:12</t>
   </si>
   <si>
     <t>MOB-TC-163</t>
@@ -2980,7 +2980,7 @@
     <t>1. Tap "Add to Calendar" on confirmation (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:49</t>
+    <t>2026-09-03 08:51:24</t>
   </si>
   <si>
     <t>MOB-TC-164</t>
@@ -2992,7 +2992,7 @@
     <t>1. View session 5 mins before start (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:00</t>
+    <t>2026-09-03 08:51:35</t>
   </si>
   <si>
     <t>MOB-TC-165</t>
@@ -3004,7 +3004,7 @@
     <t>1. Tap Cancel on booked session (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:12</t>
+    <t>2026-09-03 08:51:47</t>
   </si>
   <si>
     <t>MOB-TC-166</t>
@@ -3016,7 +3016,7 @@
     <t>1. Schedule session 2. Trigger notification alarm (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:23</t>
+    <t>2026-09-03 08:51:58</t>
   </si>
   <si>
     <t>MOB-TC-167</t>
@@ -3028,7 +3028,7 @@
     <t>1. Check schedule time display (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:35</t>
+    <t>2026-09-03 08:52:10</t>
   </si>
   <si>
     <t>MOB-TC-168</t>
@@ -3040,7 +3040,7 @@
     <t>1. Complete session time window (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:46</t>
+    <t>2026-09-03 08:52:21</t>
   </si>
   <si>
     <t>MOB-TC-169</t>
@@ -3052,7 +3052,7 @@
     <t>1. Open Availability settings 2. Toggle Mon/Tue/Thu (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:58</t>
+    <t>2026-09-03 08:52:33</t>
   </si>
   <si>
     <t>MOB-TC-170</t>
@@ -3064,7 +3064,7 @@
     <t>1. Open Schedule in offline mode (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:09</t>
+    <t>2026-09-03 08:52:44</t>
   </si>
   <si>
     <t>MOB-TC-171</t>
@@ -3076,7 +3076,7 @@
     <t>1. Toggle off Marketing alerts (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:21</t>
+    <t>2026-09-03 08:52:56</t>
   </si>
   <si>
     <t>MOB-TC-172</t>
@@ -3088,7 +3088,7 @@
     <t>1. Inspect Storage settings 2. Tap Clear Cache (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:32</t>
+    <t>2026-09-03 08:53:07</t>
   </si>
   <si>
     <t>MOB-TC-173</t>
@@ -3100,7 +3100,7 @@
     <t>1. Scroll to bottom of Settings (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:44</t>
+    <t>2026-09-03 08:53:19</t>
   </si>
   <si>
     <t>MOB-TC-174</t>
@@ -3112,7 +3112,7 @@
     <t>1. Tap Privacy Policy (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:55</t>
+    <t>2026-09-03 08:53:30</t>
   </si>
   <si>
     <t>MOB-TC-175</t>
@@ -3124,7 +3124,7 @@
     <t>1. Fill feedback form 2. Attach screenshot 3. Submit (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:07</t>
+    <t>2026-09-03 08:53:42</t>
   </si>
   <si>
     <t>MOB-TC-176</t>
@@ -3136,7 +3136,7 @@
     <t>1. Enter old password and new password 2. Save (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:18</t>
+    <t>2026-09-03 08:53:53</t>
   </si>
   <si>
     <t>MOB-TC-177</t>
@@ -3148,7 +3148,7 @@
     <t>1. Open Blocked Users 2. Tap Unblock (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:30</t>
+    <t>2026-09-03 08:54:05</t>
   </si>
   <si>
     <t>MOB-TC-178</t>
@@ -3160,7 +3160,7 @@
     <t>1. Enable 2FA 2. Enter verification code (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:41</t>
+    <t>2026-09-03 08:54:16</t>
   </si>
   <si>
     <t>MOB-TC-179</t>
@@ -3172,7 +3172,7 @@
     <t>1. Select Hindi / Spanish 2. Apply (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:53</t>
+    <t>2026-09-03 08:54:28</t>
   </si>
   <si>
     <t>MOB-TC-180</t>
@@ -3184,7 +3184,7 @@
     <t>1. Tap Delete Account 2. Confirm intent (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:04</t>
+    <t>2026-09-03 08:54:39</t>
   </si>
   <si>
     <t>MOB-TC-181</t>
@@ -3196,7 +3196,7 @@
     <t>1. Monitor React Native JS &amp; UI thread FPS (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:16</t>
+    <t>2026-09-03 08:54:51</t>
   </si>
   <si>
     <t>MOB-TC-182</t>
@@ -3208,7 +3208,7 @@
     <t>1. Background app for 5 mins 2. Resume (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:27</t>
+    <t>2026-09-03 08:55:02</t>
   </si>
   <si>
     <t>MOB-TC-183</t>
@@ -3220,7 +3220,7 @@
     <t>1. Reconnect to WiFi after offline actions (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:39</t>
+    <t>2026-09-03 08:55:14</t>
   </si>
   <si>
     <t>MOB-TC-184</t>
@@ -3232,7 +3232,7 @@
     <t>1. Browse 50 user profiles 2. Revisit same profiles (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:50</t>
+    <t>2026-09-03 08:55:25</t>
   </si>
   <si>
     <t>MOB-TC-185</t>
@@ -3244,7 +3244,7 @@
     <t>1. Simulate Android Battery Saver mode (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:02</t>
+    <t>2026-09-03 08:55:37</t>
   </si>
   <si>
     <t>MOB-TC-186</t>
@@ -3256,7 +3256,7 @@
     <t>1. Kill app process 2. Measure cold launch time (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:13</t>
+    <t>2026-09-03 08:55:48</t>
   </si>
   <si>
     <t>MOB-TC-187</t>
@@ -3268,7 +3268,7 @@
     <t>1. Switch from another app back to SkillSwap (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:25</t>
+    <t>2026-09-03 08:56:00</t>
   </si>
   <si>
     <t>MOB-TC-188</t>
@@ -3280,7 +3280,7 @@
     <t>1. Rapidly tap hardware back button 5 times (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:36</t>
+    <t>2026-09-03 08:56:11</t>
   </si>
   <si>
     <t>MOB-TC-189</t>
@@ -3292,7 +3292,7 @@
     <t>1. Tap primary buttons across screens (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:48</t>
+    <t>2026-09-03 08:56:23</t>
   </si>
   <si>
     <t>MOB-TC-190</t>
@@ -3304,7 +3304,7 @@
     <t>1. Simulate unexpected null prop render (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:59</t>
+    <t>2026-09-03 08:56:34</t>
   </si>
   <si>
     <t>MOB-TC-191</t>
@@ -3316,7 +3316,7 @@
     <t>1. Open camera feature 2. Click Deny (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:11</t>
+    <t>2026-09-03 08:56:46</t>
   </si>
   <si>
     <t>MOB-TC-192</t>
@@ -3328,7 +3328,7 @@
     <t>1. Request mic access 2. Click Allow (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:22</t>
+    <t>2026-09-03 08:56:57</t>
   </si>
   <si>
     <t>MOB-TC-193</t>
@@ -3340,7 +3340,7 @@
     <t>1. Open photo picker 2. Grant photo permission (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:34</t>
+    <t>2026-09-03 08:57:09</t>
   </si>
   <si>
     <t>MOB-TC-194</t>
@@ -3352,7 +3352,7 @@
     <t>1. Tap help link "https://skillswap.io/help" (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:45</t>
+    <t>2026-09-03 08:57:20</t>
   </si>
   <si>
     <t>MOB-TC-195</t>
@@ -3364,7 +3364,7 @@
     <t>1. Tap share swap invitation (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:57</t>
+    <t>2026-09-03 08:57:32</t>
   </si>
   <si>
     <t>MOB-TC-196</t>
@@ -3376,7 +3376,7 @@
     <t>1. During active voice note, receive phone call (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:08</t>
+    <t>2026-09-03 08:57:43</t>
   </si>
   <si>
     <t>MOB-TC-197</t>
@@ -3388,7 +3388,7 @@
     <t>1. Keep video call open for 10 minutes without touching (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:20</t>
+    <t>2026-09-03 08:57:55</t>
   </si>
   <si>
     <t>MOB-TC-198</t>
@@ -3400,7 +3400,7 @@
     <t>1. End video call session (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:31</t>
+    <t>2026-09-03 08:58:06</t>
   </si>
   <si>
     <t>MOB-TC-199</t>
@@ -3412,7 +3412,7 @@
     <t>1. Query NetInfo connection type (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:43</t>
+    <t>2026-09-03 08:58:18</t>
   </si>
   <si>
     <t>MOB-TC-200</t>
@@ -3424,7 +3424,7 @@
     <t>1. Check for OTA / bundle updates (Device: Samsung S23 (API 34))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:54</t>
+    <t>2026-09-03 08:58:29</t>
   </si>
   <si>
     <t>MOB-TC-201</t>
@@ -3436,7 +3436,7 @@
     <t>1. Launch APK 2. Observe splash animation (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:06</t>
+    <t>2026-09-03 08:58:41</t>
   </si>
   <si>
     <t>MOB-TC-202</t>
@@ -3448,7 +3448,7 @@
     <t>1. Tap password field 2. Check layout scroll (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:17</t>
+    <t>2026-09-03 08:58:52</t>
   </si>
   <si>
     <t>MOB-TC-203</t>
@@ -3460,7 +3460,7 @@
     <t>1. Tap Biometric Login 2. Emulate fingerprint match (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:29</t>
+    <t>2026-09-03 08:59:04</t>
   </si>
   <si>
     <t>MOB-TC-204</t>
@@ -3472,7 +3472,7 @@
     <t>1. Tap Google Auth button (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:40</t>
+    <t>2026-09-03 08:59:15</t>
   </si>
   <si>
     <t>MOB-TC-205</t>
@@ -3484,7 +3484,7 @@
     <t>1. Swipe left on skill categories carousel (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:52</t>
+    <t>2026-09-03 08:59:27</t>
   </si>
   <si>
     <t>MOB-TC-206</t>
@@ -3496,7 +3496,7 @@
     <t>1. Tap "JavaScript" chip (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:03</t>
+    <t>2026-09-03 08:59:38</t>
   </si>
   <si>
     <t>MOB-TC-207</t>
@@ -3508,7 +3508,7 @@
     <t>1. On Step 2 of Onboarding, press Back button (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:15</t>
+    <t>2026-09-03 08:59:50</t>
   </si>
   <si>
     <t>MOB-TC-208</t>
@@ -3520,7 +3520,7 @@
     <t>1. Press back twice on Landing (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:26</t>
+    <t>2026-09-03 09:00:01</t>
   </si>
   <si>
     <t>MOB-TC-209</t>
@@ -3532,7 +3532,7 @@
     <t>1. Type password 2. Toggle secureTextEntry (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:38</t>
+    <t>2026-09-03 09:00:13</t>
   </si>
   <si>
     <t>MOB-TC-210</t>
@@ -3544,7 +3544,7 @@
     <t>1. Open skillswap://auth/verify?token=xyz (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:49</t>
+    <t>2026-09-03 09:00:24</t>
   </si>
   <si>
     <t>MOB-TC-211</t>
@@ -3556,7 +3556,7 @@
     <t>1. Tap bottom navigation icons sequentially (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:01</t>
+    <t>2026-09-03 09:00:36</t>
   </si>
   <si>
     <t>MOB-TC-212</t>
@@ -3568,7 +3568,7 @@
     <t>1. Receive unread message (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:12</t>
+    <t>2026-09-03 09:00:47</t>
   </si>
   <si>
     <t>MOB-TC-213</t>
@@ -3580,7 +3580,7 @@
     <t>1. Drag down from top of Home screen (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:24</t>
+    <t>2026-09-03 09:00:59</t>
   </si>
   <si>
     <t>MOB-TC-214</t>
@@ -3592,7 +3592,7 @@
     <t>1. Open Filter sheet 2. Drag handle down (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:35</t>
+    <t>2026-09-03 09:01:10</t>
   </si>
   <si>
     <t>MOB-TC-215</t>
@@ -3604,7 +3604,7 @@
     <t>1. Open User Detail 2. Tap &lt; back arrow in Header (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:47</t>
+    <t>2026-09-03 09:01:22</t>
   </si>
   <si>
     <t>MOB-TC-216</t>
@@ -3616,7 +3616,7 @@
     <t>1. Scroll feed down 2. Double tap Home tab icon (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:58</t>
+    <t>2026-09-03 09:01:33</t>
   </si>
   <si>
     <t>MOB-TC-217</t>
@@ -3628,7 +3628,7 @@
     <t>1. Verify padding on top and bottom edges (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:10</t>
+    <t>2026-09-03 09:01:45</t>
   </si>
   <si>
     <t>MOB-TC-218</t>
@@ -3640,7 +3640,7 @@
     <t>1. Rotate device to Landscape 90 deg (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:21</t>
+    <t>2026-09-03 09:01:56</t>
   </si>
   <si>
     <t>MOB-TC-219</t>
@@ -3652,7 +3652,7 @@
     <t>1. Increase system font size to Large (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:33</t>
+    <t>2026-09-03 09:02:08</t>
   </si>
   <si>
     <t>MOB-TC-220</t>
@@ -3664,7 +3664,7 @@
     <t>1. Toggle Android Dark Mode in quick settings (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:44</t>
+    <t>2026-09-03 09:02:19</t>
   </si>
   <si>
     <t>MOB-TC-221</t>
@@ -3676,7 +3676,7 @@
     <t>1. Rapidly type "Graphic Design" (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:56</t>
+    <t>2026-09-03 09:02:31</t>
   </si>
   <si>
     <t>MOB-TC-222</t>
@@ -3688,7 +3688,7 @@
     <t>1. Flick category chips row horizontally (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:07</t>
+    <t>2026-09-03 09:02:42</t>
   </si>
   <si>
     <t>MOB-TC-223</t>
@@ -3700,7 +3700,7 @@
     <t>1. Press down on peer card (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:19</t>
+    <t>2026-09-03 09:02:54</t>
   </si>
   <si>
     <t>MOB-TC-224</t>
@@ -3712,7 +3712,7 @@
     <t>1. Tap bookmark star on mentor card (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:30</t>
+    <t>2026-09-03 09:03:05</t>
   </si>
   <si>
     <t>MOB-TC-225</t>
@@ -3724,7 +3724,7 @@
     <t>1. Tap "Find Mentors Near Me" (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:42</t>
+    <t>2026-09-03 09:03:17</t>
   </si>
   <si>
     <t>MOB-TC-226</t>
@@ -3736,7 +3736,7 @@
     <t>1. Inspect match card location tag (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:53</t>
+    <t>2026-09-03 09:03:28</t>
   </si>
   <si>
     <t>MOB-TC-227</t>
@@ -3748,7 +3748,7 @@
     <t>1. Rapidly scroll 100 mentor cards (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:05</t>
+    <t>2026-09-03 09:03:40</t>
   </si>
   <si>
     <t>MOB-TC-228</t>
@@ -3760,7 +3760,7 @@
     <t>1. Search unavailable term (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:16</t>
+    <t>2026-09-03 09:03:51</t>
   </si>
   <si>
     <t>MOB-TC-229</t>
@@ -3772,7 +3772,7 @@
     <t>1. Tap share icon on profile (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:28</t>
+    <t>2026-09-03 09:04:03</t>
   </si>
   <si>
     <t>MOB-TC-230</t>
@@ -3784,7 +3784,7 @@
     <t>1. Tap multiple skill tags in filter modal (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:39</t>
+    <t>2026-09-03 09:04:14</t>
   </si>
   <si>
     <t>MOB-TC-231</t>
@@ -3796,7 +3796,7 @@
     <t>1. Send message from web to mobile user (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:51</t>
+    <t>2026-09-03 09:04:26</t>
   </si>
   <si>
     <t>MOB-TC-232</t>
@@ -3808,7 +3808,7 @@
     <t>1. Tap text input in chat screen (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:02</t>
+    <t>2026-09-03 09:04:37</t>
   </si>
   <si>
     <t>MOB-TC-233</t>
@@ -3820,7 +3820,7 @@
     <t>1. Long press microphone icon 2. Release to send (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:14</t>
+    <t>2026-09-03 09:04:49</t>
   </si>
   <si>
     <t>MOB-TC-234</t>
@@ -3832,7 +3832,7 @@
     <t>1. Press mic 2. Swipe left towards trash icon (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:25</t>
+    <t>2026-09-03 09:05:00</t>
   </si>
   <si>
     <t>MOB-TC-235</t>
@@ -3844,7 +3844,7 @@
     <t>1. Tap camera icon 2. Select image from gallery (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:37</t>
+    <t>2026-09-03 09:05:12</t>
   </si>
   <si>
     <t>MOB-TC-236</t>
@@ -3856,7 +3856,7 @@
     <t>1. Long press incoming message bubble (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:48</t>
+    <t>2026-09-03 09:05:23</t>
   </si>
   <si>
     <t>MOB-TC-237</t>
@@ -3868,7 +3868,7 @@
     <t>1. Tap Reply on message (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:00</t>
+    <t>2026-09-03 09:05:35</t>
   </si>
   <si>
     <t>MOB-TC-238</t>
@@ -3880,7 +3880,7 @@
     <t>1. Scroll up 500px 2. Receive new message (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:11</t>
+    <t>2026-09-03 09:05:46</t>
   </si>
   <si>
     <t>MOB-TC-239</t>
@@ -3892,7 +3892,7 @@
     <t>1. Send "https://github.com" (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:23</t>
+    <t>2026-09-03 09:05:58</t>
   </si>
   <si>
     <t>MOB-TC-240</t>
@@ -3904,7 +3904,7 @@
     <t>1. Turn on Airplane mode 2. Send message (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:34</t>
+    <t>2026-09-03 09:06:09</t>
   </si>
   <si>
     <t>MOB-TC-241</t>
@@ -3916,7 +3916,7 @@
     <t>1. Trigger incoming call socket event (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:46</t>
+    <t>2026-09-03 09:06:21</t>
   </si>
   <si>
     <t>MOB-TC-242</t>
@@ -3928,7 +3928,7 @@
     <t>1. Tap camera switch icon in call toolbar (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:57</t>
+    <t>2026-09-03 09:06:32</t>
   </si>
   <si>
     <t>MOB-TC-243</t>
@@ -3940,7 +3940,7 @@
     <t>1. Cover proximity sensor (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:09</t>
+    <t>2026-09-03 09:06:44</t>
   </si>
   <si>
     <t>MOB-TC-244</t>
@@ -3952,7 +3952,7 @@
     <t>1. In active call, press Home button (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:20</t>
+    <t>2026-09-03 09:06:55</t>
   </si>
   <si>
     <t>MOB-TC-245</t>
@@ -3964,7 +3964,7 @@
     <t>1. Tap audio route button 2. Select Speaker (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:32</t>
+    <t>2026-09-03 09:07:07</t>
   </si>
   <si>
     <t>MOB-TC-246</t>
@@ -3976,7 +3976,7 @@
     <t>1. Tap collapse arrow in call header (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:43</t>
+    <t>2026-09-03 09:07:18</t>
   </si>
   <si>
     <t>MOB-TC-247</t>
@@ -3988,7 +3988,7 @@
     <t>1. Simulate high packet loss (&gt;20%) (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:55</t>
+    <t>2026-09-03 09:07:30</t>
   </si>
   <si>
     <t>MOB-TC-248</t>
@@ -4000,7 +4000,7 @@
     <t>1. Toggle WiFi off during call (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:06</t>
+    <t>2026-09-03 09:07:41</t>
   </si>
   <si>
     <t>MOB-TC-249</t>
@@ -4012,7 +4012,7 @@
     <t>1. Tap red end call button (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:18</t>
+    <t>2026-09-03 09:07:53</t>
   </si>
   <si>
     <t>MOB-TC-250</t>
@@ -4024,7 +4024,7 @@
     <t>1. Complete call session (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:29</t>
+    <t>2026-09-03 09:08:04</t>
   </si>
   <si>
     <t>MOB-TC-251</t>
@@ -4036,7 +4036,7 @@
     <t>1. Tap avatar camera icon 2. Capture photo (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:41</t>
+    <t>2026-09-03 09:08:16</t>
   </si>
   <si>
     <t>MOB-TC-252</t>
@@ -4048,7 +4048,7 @@
     <t>1. Tap Add Skill 2. Select Level 4/5 (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:52</t>
+    <t>2026-09-03 09:08:27</t>
   </si>
   <si>
     <t>MOB-TC-253</t>
@@ -4060,7 +4060,7 @@
     <t>1. Type headline in profile edit (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:04</t>
+    <t>2026-09-03 09:08:39</t>
   </si>
   <si>
     <t>MOB-TC-254</t>
@@ -4072,7 +4072,7 @@
     <t>1. Scroll to Badges horizontal slider (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:15</t>
+    <t>2026-09-03 09:08:50</t>
   </si>
   <si>
     <t>MOB-TC-255</t>
@@ -4084,7 +4084,7 @@
     <t>1. Tap portfolio image 2. Pinch with two fingers (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:27</t>
+    <t>2026-09-03 09:09:02</t>
   </si>
   <si>
     <t>MOB-TC-256</t>
@@ -4096,7 +4096,7 @@
     <t>1. Tap swap balance card in profile (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:38</t>
+    <t>2026-09-03 09:09:13</t>
   </si>
   <si>
     <t>MOB-TC-257</t>
@@ -4108,7 +4108,7 @@
     <t>1. Tap "Preview as Public" (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:50</t>
+    <t>2026-09-03 09:09:25</t>
   </si>
   <si>
     <t>MOB-TC-258</t>
@@ -4120,7 +4120,7 @@
     <t>1. Tap "Copy Link" (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:01</t>
+    <t>2026-09-03 09:09:36</t>
   </si>
   <si>
     <t>MOB-TC-259</t>
@@ -4132,7 +4132,7 @@
     <t>1. Tap "5 Stars" filter chip in reviews (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:13</t>
+    <t>2026-09-03 09:09:48</t>
   </si>
   <si>
     <t>MOB-TC-260</t>
@@ -4144,7 +4144,7 @@
     <t>1. Tap Logout in settings (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:24</t>
+    <t>2026-09-03 09:09:59</t>
   </si>
   <si>
     <t>MOB-TC-261</t>
@@ -4156,7 +4156,7 @@
     <t>1. Swipe horizontal calendar days strip (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:36</t>
+    <t>2026-09-03 09:10:11</t>
   </si>
   <si>
     <t>MOB-TC-262</t>
@@ -4168,7 +4168,7 @@
     <t>1. Pick mentor slot 2. Tap 3:30 PM (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:47</t>
+    <t>2026-09-03 09:10:22</t>
   </si>
   <si>
     <t>MOB-TC-263</t>
@@ -4180,7 +4180,7 @@
     <t>1. Tap "Add to Calendar" on confirmation (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:59</t>
+    <t>2026-09-03 09:10:34</t>
   </si>
   <si>
     <t>MOB-TC-264</t>
@@ -4192,7 +4192,7 @@
     <t>1. View session 5 mins before start (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:10</t>
+    <t>2026-09-03 09:10:45</t>
   </si>
   <si>
     <t>MOB-TC-265</t>
@@ -4204,7 +4204,7 @@
     <t>1. Tap Cancel on booked session (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:22</t>
+    <t>2026-09-03 09:10:57</t>
   </si>
   <si>
     <t>MOB-TC-266</t>
@@ -4216,7 +4216,7 @@
     <t>1. Schedule session 2. Trigger notification alarm (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:33</t>
+    <t>2026-09-03 09:11:08</t>
   </si>
   <si>
     <t>MOB-TC-267</t>
@@ -4228,7 +4228,7 @@
     <t>1. Check schedule time display (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:45</t>
+    <t>2026-09-03 09:11:20</t>
   </si>
   <si>
     <t>MOB-TC-268</t>
@@ -4240,7 +4240,7 @@
     <t>1. Complete session time window (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:56</t>
+    <t>2026-09-03 09:11:31</t>
   </si>
   <si>
     <t>MOB-TC-269</t>
@@ -4252,7 +4252,7 @@
     <t>1. Open Availability settings 2. Toggle Mon/Tue/Thu (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:08</t>
+    <t>2026-09-03 09:11:43</t>
   </si>
   <si>
     <t>MOB-TC-270</t>
@@ -4264,7 +4264,7 @@
     <t>1. Open Schedule in offline mode (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:19</t>
+    <t>2026-09-03 09:11:54</t>
   </si>
   <si>
     <t>MOB-TC-271</t>
@@ -4276,7 +4276,7 @@
     <t>1. Toggle off Marketing alerts (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:31</t>
+    <t>2026-09-03 09:12:06</t>
   </si>
   <si>
     <t>MOB-TC-272</t>
@@ -4288,7 +4288,7 @@
     <t>1. Inspect Storage settings 2. Tap Clear Cache (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:42</t>
+    <t>2026-09-03 09:12:17</t>
   </si>
   <si>
     <t>MOB-TC-273</t>
@@ -4300,7 +4300,7 @@
     <t>1. Scroll to bottom of Settings (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:54</t>
+    <t>2026-09-03 09:12:29</t>
   </si>
   <si>
     <t>MOB-TC-274</t>
@@ -4312,7 +4312,7 @@
     <t>1. Tap Privacy Policy (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:05</t>
+    <t>2026-09-03 09:12:40</t>
   </si>
   <si>
     <t>MOB-TC-275</t>
@@ -4324,7 +4324,7 @@
     <t>1. Fill feedback form 2. Attach screenshot 3. Submit (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:17</t>
+    <t>2026-09-03 09:12:52</t>
   </si>
   <si>
     <t>MOB-TC-276</t>
@@ -4336,7 +4336,7 @@
     <t>1. Enter old password and new password 2. Save (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:28</t>
+    <t>2026-09-03 09:13:03</t>
   </si>
   <si>
     <t>MOB-TC-277</t>
@@ -4348,7 +4348,7 @@
     <t>1. Open Blocked Users 2. Tap Unblock (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:40</t>
+    <t>2026-09-03 09:13:15</t>
   </si>
   <si>
     <t>MOB-TC-278</t>
@@ -4360,7 +4360,7 @@
     <t>1. Enable 2FA 2. Enter verification code (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:51</t>
+    <t>2026-09-03 09:13:26</t>
   </si>
   <si>
     <t>MOB-TC-279</t>
@@ -4372,7 +4372,7 @@
     <t>1. Select Hindi / Spanish 2. Apply (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:03</t>
+    <t>2026-09-03 09:13:38</t>
   </si>
   <si>
     <t>MOB-TC-280</t>
@@ -4384,7 +4384,7 @@
     <t>1. Tap Delete Account 2. Confirm intent (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:14</t>
+    <t>2026-09-03 09:13:49</t>
   </si>
   <si>
     <t>MOB-TC-281</t>
@@ -4396,7 +4396,7 @@
     <t>1. Monitor React Native JS &amp; UI thread FPS (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:26</t>
+    <t>2026-09-03 09:14:01</t>
   </si>
   <si>
     <t>MOB-TC-282</t>
@@ -4408,7 +4408,7 @@
     <t>1. Background app for 5 mins 2. Resume (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:37</t>
+    <t>2026-09-03 09:14:12</t>
   </si>
   <si>
     <t>MOB-TC-283</t>
@@ -4420,7 +4420,7 @@
     <t>1. Reconnect to WiFi after offline actions (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:49</t>
+    <t>2026-09-03 09:14:24</t>
   </si>
   <si>
     <t>MOB-TC-284</t>
@@ -4432,7 +4432,7 @@
     <t>1. Browse 50 user profiles 2. Revisit same profiles (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:00</t>
+    <t>2026-09-03 09:14:35</t>
   </si>
   <si>
     <t>MOB-TC-285</t>
@@ -4444,7 +4444,7 @@
     <t>1. Simulate Android Battery Saver mode (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:12</t>
+    <t>2026-09-03 09:14:47</t>
   </si>
   <si>
     <t>MOB-TC-286</t>
@@ -4456,7 +4456,7 @@
     <t>1. Kill app process 2. Measure cold launch time (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:23</t>
+    <t>2026-09-03 09:14:58</t>
   </si>
   <si>
     <t>MOB-TC-287</t>
@@ -4468,7 +4468,7 @@
     <t>1. Switch from another app back to SkillSwap (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:35</t>
+    <t>2026-09-03 09:15:10</t>
   </si>
   <si>
     <t>MOB-TC-288</t>
@@ -4480,7 +4480,7 @@
     <t>1. Rapidly tap hardware back button 5 times (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:46</t>
+    <t>2026-09-03 09:15:21</t>
   </si>
   <si>
     <t>MOB-TC-289</t>
@@ -4492,7 +4492,7 @@
     <t>1. Tap primary buttons across screens (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:58</t>
+    <t>2026-09-03 09:15:33</t>
   </si>
   <si>
     <t>MOB-TC-290</t>
@@ -4504,7 +4504,7 @@
     <t>1. Simulate unexpected null prop render (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:09</t>
+    <t>2026-09-03 09:15:44</t>
   </si>
   <si>
     <t>MOB-TC-291</t>
@@ -4516,7 +4516,7 @@
     <t>1. Open camera feature 2. Click Deny (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:21</t>
+    <t>2026-09-03 09:15:56</t>
   </si>
   <si>
     <t>MOB-TC-292</t>
@@ -4528,7 +4528,7 @@
     <t>1. Request mic access 2. Click Allow (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:32</t>
+    <t>2026-09-03 09:16:07</t>
   </si>
   <si>
     <t>MOB-TC-293</t>
@@ -4540,7 +4540,7 @@
     <t>1. Open photo picker 2. Grant photo permission (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:44</t>
+    <t>2026-09-03 09:16:19</t>
   </si>
   <si>
     <t>MOB-TC-294</t>
@@ -4552,7 +4552,7 @@
     <t>1. Tap help link "https://skillswap.io/help" (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:55</t>
+    <t>2026-09-03 09:16:30</t>
   </si>
   <si>
     <t>MOB-TC-295</t>
@@ -4564,7 +4564,7 @@
     <t>1. Tap share swap invitation (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:07</t>
+    <t>2026-09-03 09:16:42</t>
   </si>
   <si>
     <t>MOB-TC-296</t>
@@ -4576,7 +4576,7 @@
     <t>1. During active voice note, receive phone call (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:18</t>
+    <t>2026-09-03 09:16:53</t>
   </si>
   <si>
     <t>MOB-TC-297</t>
@@ -4588,7 +4588,7 @@
     <t>1. Keep video call open for 10 minutes without touching (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:30</t>
+    <t>2026-09-03 09:17:05</t>
   </si>
   <si>
     <t>MOB-TC-298</t>
@@ -4600,7 +4600,7 @@
     <t>1. End video call session (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:41</t>
+    <t>2026-09-03 09:17:16</t>
   </si>
   <si>
     <t>MOB-TC-299</t>
@@ -4612,7 +4612,7 @@
     <t>1. Query NetInfo connection type (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:53</t>
+    <t>2026-09-03 09:17:28</t>
   </si>
   <si>
     <t>MOB-TC-300</t>
@@ -4624,7 +4624,7 @@
     <t>1. Check for OTA / bundle updates (Device: Moto G Power (2GB RAM Profile))</t>
   </si>
   <si>
-    <t>2026-09-03 09:10:04</t>
+    <t>2026-09-03 09:17:39</t>
   </si>
 </sst>
 </file>
@@ -5166,7 +5166,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -5207,7 +5207,7 @@
         <v>30</v>
       </c>
       <c r="J3" s="5">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>22</v>
@@ -5289,7 +5289,7 @@
         <v>45</v>
       </c>
       <c r="J5" s="5">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>22</v>
@@ -5330,7 +5330,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>22</v>
@@ -5412,7 +5412,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>22</v>
@@ -5453,7 +5453,7 @@
         <v>74</v>
       </c>
       <c r="J9" s="5">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>22</v>
@@ -5494,7 +5494,7 @@
         <v>81</v>
       </c>
       <c r="J10" s="2">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>22</v>
@@ -5535,7 +5535,7 @@
         <v>88</v>
       </c>
       <c r="J11" s="5">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>22</v>
@@ -5576,7 +5576,7 @@
         <v>97</v>
       </c>
       <c r="J12" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>22</v>
@@ -5617,7 +5617,7 @@
         <v>104</v>
       </c>
       <c r="J13" s="5">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>22</v>
@@ -5658,7 +5658,7 @@
         <v>111</v>
       </c>
       <c r="J14" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>22</v>
@@ -5699,7 +5699,7 @@
         <v>118</v>
       </c>
       <c r="J15" s="5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>22</v>
@@ -5740,7 +5740,7 @@
         <v>125</v>
       </c>
       <c r="J16" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>22</v>
@@ -5781,7 +5781,7 @@
         <v>132</v>
       </c>
       <c r="J17" s="5">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>22</v>
@@ -5822,7 +5822,7 @@
         <v>139</v>
       </c>
       <c r="J18" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>22</v>
@@ -5863,7 +5863,7 @@
         <v>146</v>
       </c>
       <c r="J19" s="5">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>22</v>
@@ -5904,7 +5904,7 @@
         <v>153</v>
       </c>
       <c r="J20" s="2">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>22</v>
@@ -5945,7 +5945,7 @@
         <v>160</v>
       </c>
       <c r="J21" s="5">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>22</v>
@@ -5986,7 +5986,7 @@
         <v>169</v>
       </c>
       <c r="J22" s="2">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>22</v>
@@ -6027,7 +6027,7 @@
         <v>176</v>
       </c>
       <c r="J23" s="5">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>22</v>
@@ -6068,7 +6068,7 @@
         <v>183</v>
       </c>
       <c r="J24" s="2">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>22</v>
@@ -6109,7 +6109,7 @@
         <v>190</v>
       </c>
       <c r="J25" s="5">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>22</v>
@@ -6150,7 +6150,7 @@
         <v>197</v>
       </c>
       <c r="J26" s="2">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>22</v>
@@ -6191,7 +6191,7 @@
         <v>204</v>
       </c>
       <c r="J27" s="5">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>22</v>
@@ -6232,7 +6232,7 @@
         <v>211</v>
       </c>
       <c r="J28" s="2">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>22</v>
@@ -6273,7 +6273,7 @@
         <v>218</v>
       </c>
       <c r="J29" s="5">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>22</v>
@@ -6314,7 +6314,7 @@
         <v>225</v>
       </c>
       <c r="J30" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>22</v>
@@ -6355,7 +6355,7 @@
         <v>232</v>
       </c>
       <c r="J31" s="5">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>22</v>
@@ -6396,7 +6396,7 @@
         <v>241</v>
       </c>
       <c r="J32" s="2">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>22</v>
@@ -6437,7 +6437,7 @@
         <v>248</v>
       </c>
       <c r="J33" s="5">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>22</v>
@@ -6478,7 +6478,7 @@
         <v>255</v>
       </c>
       <c r="J34" s="2">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>22</v>
@@ -6519,7 +6519,7 @@
         <v>262</v>
       </c>
       <c r="J35" s="5">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>22</v>
@@ -6560,7 +6560,7 @@
         <v>269</v>
       </c>
       <c r="J36" s="2">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>22</v>
@@ -6601,7 +6601,7 @@
         <v>276</v>
       </c>
       <c r="J37" s="5">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>22</v>
@@ -6642,7 +6642,7 @@
         <v>283</v>
       </c>
       <c r="J38" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>22</v>
@@ -6683,7 +6683,7 @@
         <v>290</v>
       </c>
       <c r="J39" s="5">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>22</v>
@@ -6724,7 +6724,7 @@
         <v>297</v>
       </c>
       <c r="J40" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>22</v>
@@ -6765,7 +6765,7 @@
         <v>304</v>
       </c>
       <c r="J41" s="5">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>22</v>
@@ -6847,7 +6847,7 @@
         <v>320</v>
       </c>
       <c r="J43" s="5">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>22</v>
@@ -6888,7 +6888,7 @@
         <v>327</v>
       </c>
       <c r="J44" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>22</v>
@@ -6929,7 +6929,7 @@
         <v>334</v>
       </c>
       <c r="J45" s="5">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>22</v>
@@ -6970,7 +6970,7 @@
         <v>341</v>
       </c>
       <c r="J46" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>22</v>
@@ -7011,7 +7011,7 @@
         <v>348</v>
       </c>
       <c r="J47" s="5">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>22</v>
@@ -7052,7 +7052,7 @@
         <v>355</v>
       </c>
       <c r="J48" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>22</v>
@@ -7093,7 +7093,7 @@
         <v>362</v>
       </c>
       <c r="J49" s="5">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>22</v>
@@ -7134,7 +7134,7 @@
         <v>369</v>
       </c>
       <c r="J50" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>22</v>
@@ -7175,7 +7175,7 @@
         <v>376</v>
       </c>
       <c r="J51" s="5">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>22</v>
@@ -7216,7 +7216,7 @@
         <v>385</v>
       </c>
       <c r="J52" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>22</v>
@@ -7257,7 +7257,7 @@
         <v>392</v>
       </c>
       <c r="J53" s="5">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>22</v>
@@ -7298,7 +7298,7 @@
         <v>399</v>
       </c>
       <c r="J54" s="2">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>22</v>
@@ -7339,7 +7339,7 @@
         <v>406</v>
       </c>
       <c r="J55" s="5">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>22</v>
@@ -7380,7 +7380,7 @@
         <v>413</v>
       </c>
       <c r="J56" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>22</v>
@@ -7421,7 +7421,7 @@
         <v>420</v>
       </c>
       <c r="J57" s="5">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>22</v>
@@ -7462,7 +7462,7 @@
         <v>427</v>
       </c>
       <c r="J58" s="2">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>22</v>
@@ -7503,7 +7503,7 @@
         <v>434</v>
       </c>
       <c r="J59" s="5">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>22</v>
@@ -7544,7 +7544,7 @@
         <v>441</v>
       </c>
       <c r="J60" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>22</v>
@@ -7585,7 +7585,7 @@
         <v>448</v>
       </c>
       <c r="J61" s="5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>22</v>
@@ -7626,7 +7626,7 @@
         <v>457</v>
       </c>
       <c r="J62" s="2">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>22</v>
@@ -7667,7 +7667,7 @@
         <v>464</v>
       </c>
       <c r="J63" s="5">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>22</v>
@@ -7708,7 +7708,7 @@
         <v>471</v>
       </c>
       <c r="J64" s="2">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>22</v>
@@ -7749,7 +7749,7 @@
         <v>478</v>
       </c>
       <c r="J65" s="5">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>22</v>
@@ -7790,7 +7790,7 @@
         <v>485</v>
       </c>
       <c r="J66" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>22</v>
@@ -7831,7 +7831,7 @@
         <v>492</v>
       </c>
       <c r="J67" s="5">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>22</v>
@@ -7872,7 +7872,7 @@
         <v>499</v>
       </c>
       <c r="J68" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>22</v>
@@ -7913,7 +7913,7 @@
         <v>506</v>
       </c>
       <c r="J69" s="5">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>22</v>
@@ -7954,7 +7954,7 @@
         <v>513</v>
       </c>
       <c r="J70" s="2">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>22</v>
@@ -7995,7 +7995,7 @@
         <v>520</v>
       </c>
       <c r="J71" s="5">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>22</v>
@@ -8036,7 +8036,7 @@
         <v>529</v>
       </c>
       <c r="J72" s="2">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>22</v>
@@ -8077,7 +8077,7 @@
         <v>536</v>
       </c>
       <c r="J73" s="5">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>22</v>
@@ -8118,7 +8118,7 @@
         <v>543</v>
       </c>
       <c r="J74" s="2">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>22</v>
@@ -8159,7 +8159,7 @@
         <v>550</v>
       </c>
       <c r="J75" s="5">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>22</v>
@@ -8200,7 +8200,7 @@
         <v>557</v>
       </c>
       <c r="J76" s="2">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>22</v>
@@ -8241,7 +8241,7 @@
         <v>564</v>
       </c>
       <c r="J77" s="5">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>22</v>
@@ -8282,7 +8282,7 @@
         <v>571</v>
       </c>
       <c r="J78" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>22</v>
@@ -8323,7 +8323,7 @@
         <v>578</v>
       </c>
       <c r="J79" s="5">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>22</v>
@@ -8364,7 +8364,7 @@
         <v>585</v>
       </c>
       <c r="J80" s="2">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>22</v>
@@ -8405,7 +8405,7 @@
         <v>592</v>
       </c>
       <c r="J81" s="5">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>22</v>
@@ -8446,7 +8446,7 @@
         <v>601</v>
       </c>
       <c r="J82" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>22</v>
@@ -8487,7 +8487,7 @@
         <v>608</v>
       </c>
       <c r="J83" s="5">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>22</v>
@@ -8528,7 +8528,7 @@
         <v>615</v>
       </c>
       <c r="J84" s="2">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>22</v>
@@ -8610,7 +8610,7 @@
         <v>629</v>
       </c>
       <c r="J86" s="2">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>22</v>
@@ -8651,7 +8651,7 @@
         <v>636</v>
       </c>
       <c r="J87" s="5">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>22</v>
@@ -8692,7 +8692,7 @@
         <v>643</v>
       </c>
       <c r="J88" s="2">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>22</v>
@@ -8733,7 +8733,7 @@
         <v>650</v>
       </c>
       <c r="J89" s="5">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>22</v>
@@ -8774,7 +8774,7 @@
         <v>657</v>
       </c>
       <c r="J90" s="2">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>22</v>
@@ -8815,7 +8815,7 @@
         <v>664</v>
       </c>
       <c r="J91" s="5">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>22</v>
@@ -8856,7 +8856,7 @@
         <v>673</v>
       </c>
       <c r="J92" s="2">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>22</v>
@@ -8897,7 +8897,7 @@
         <v>680</v>
       </c>
       <c r="J93" s="5">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>22</v>
@@ -8938,7 +8938,7 @@
         <v>687</v>
       </c>
       <c r="J94" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>22</v>
@@ -8979,7 +8979,7 @@
         <v>694</v>
       </c>
       <c r="J95" s="5">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>22</v>
@@ -9020,7 +9020,7 @@
         <v>701</v>
       </c>
       <c r="J96" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>22</v>
@@ -9102,7 +9102,7 @@
         <v>715</v>
       </c>
       <c r="J98" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>22</v>
@@ -9143,7 +9143,7 @@
         <v>722</v>
       </c>
       <c r="J99" s="5">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>22</v>
@@ -9184,7 +9184,7 @@
         <v>729</v>
       </c>
       <c r="J100" s="2">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>22</v>
@@ -9225,7 +9225,7 @@
         <v>736</v>
       </c>
       <c r="J101" s="5">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>22</v>
@@ -9266,7 +9266,7 @@
         <v>21</v>
       </c>
       <c r="J102" s="2">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>22</v>
@@ -9307,7 +9307,7 @@
         <v>30</v>
       </c>
       <c r="J103" s="5">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>22</v>
@@ -9348,7 +9348,7 @@
         <v>38</v>
       </c>
       <c r="J104" s="2">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>22</v>
@@ -9389,7 +9389,7 @@
         <v>45</v>
       </c>
       <c r="J105" s="5">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>22</v>
@@ -9430,7 +9430,7 @@
         <v>52</v>
       </c>
       <c r="J106" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>22</v>
@@ -9471,7 +9471,7 @@
         <v>60</v>
       </c>
       <c r="J107" s="5">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>22</v>
@@ -9512,7 +9512,7 @@
         <v>67</v>
       </c>
       <c r="J108" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>22</v>
@@ -9553,7 +9553,7 @@
         <v>74</v>
       </c>
       <c r="J109" s="5">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>22</v>
@@ -9594,7 +9594,7 @@
         <v>81</v>
       </c>
       <c r="J110" s="2">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>22</v>
@@ -9635,7 +9635,7 @@
         <v>88</v>
       </c>
       <c r="J111" s="5">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>22</v>
@@ -9676,7 +9676,7 @@
         <v>97</v>
       </c>
       <c r="J112" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>22</v>
@@ -9717,7 +9717,7 @@
         <v>104</v>
       </c>
       <c r="J113" s="5">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>22</v>
@@ -9758,7 +9758,7 @@
         <v>111</v>
       </c>
       <c r="J114" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>22</v>
@@ -9799,7 +9799,7 @@
         <v>118</v>
       </c>
       <c r="J115" s="5">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>22</v>
@@ -9840,7 +9840,7 @@
         <v>125</v>
       </c>
       <c r="J116" s="2">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>22</v>
@@ -9881,7 +9881,7 @@
         <v>132</v>
       </c>
       <c r="J117" s="5">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>22</v>
@@ -9922,7 +9922,7 @@
         <v>139</v>
       </c>
       <c r="J118" s="2">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>22</v>
@@ -9963,7 +9963,7 @@
         <v>146</v>
       </c>
       <c r="J119" s="5">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>22</v>
@@ -10004,7 +10004,7 @@
         <v>153</v>
       </c>
       <c r="J120" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>22</v>
@@ -10045,7 +10045,7 @@
         <v>160</v>
       </c>
       <c r="J121" s="5">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>22</v>
@@ -10086,7 +10086,7 @@
         <v>169</v>
       </c>
       <c r="J122" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>22</v>
@@ -10127,7 +10127,7 @@
         <v>176</v>
       </c>
       <c r="J123" s="5">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K123" s="4" t="s">
         <v>22</v>
@@ -10168,7 +10168,7 @@
         <v>183</v>
       </c>
       <c r="J124" s="2">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>22</v>
@@ -10209,7 +10209,7 @@
         <v>190</v>
       </c>
       <c r="J125" s="5">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>22</v>
@@ -10250,7 +10250,7 @@
         <v>197</v>
       </c>
       <c r="J126" s="2">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>22</v>
@@ -10291,7 +10291,7 @@
         <v>204</v>
       </c>
       <c r="J127" s="5">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>22</v>
@@ -10332,7 +10332,7 @@
         <v>211</v>
       </c>
       <c r="J128" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>22</v>
@@ -10373,7 +10373,7 @@
         <v>218</v>
       </c>
       <c r="J129" s="5">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>22</v>
@@ -10414,7 +10414,7 @@
         <v>225</v>
       </c>
       <c r="J130" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>22</v>
@@ -10455,7 +10455,7 @@
         <v>232</v>
       </c>
       <c r="J131" s="5">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>22</v>
@@ -10496,7 +10496,7 @@
         <v>241</v>
       </c>
       <c r="J132" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>22</v>
@@ -10537,7 +10537,7 @@
         <v>248</v>
       </c>
       <c r="J133" s="5">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>22</v>
@@ -10578,7 +10578,7 @@
         <v>255</v>
       </c>
       <c r="J134" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>22</v>
@@ -10619,7 +10619,7 @@
         <v>262</v>
       </c>
       <c r="J135" s="5">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>22</v>
@@ -10660,7 +10660,7 @@
         <v>269</v>
       </c>
       <c r="J136" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>22</v>
@@ -10701,7 +10701,7 @@
         <v>276</v>
       </c>
       <c r="J137" s="5">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>22</v>
@@ -10742,7 +10742,7 @@
         <v>283</v>
       </c>
       <c r="J138" s="2">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>22</v>
@@ -10783,7 +10783,7 @@
         <v>290</v>
       </c>
       <c r="J139" s="5">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>22</v>
@@ -10824,7 +10824,7 @@
         <v>297</v>
       </c>
       <c r="J140" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>22</v>
@@ -10865,7 +10865,7 @@
         <v>304</v>
       </c>
       <c r="J141" s="5">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>22</v>
@@ -10947,7 +10947,7 @@
         <v>320</v>
       </c>
       <c r="J143" s="5">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>22</v>
@@ -10988,7 +10988,7 @@
         <v>327</v>
       </c>
       <c r="J144" s="2">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>22</v>
@@ -11029,7 +11029,7 @@
         <v>334</v>
       </c>
       <c r="J145" s="5">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>22</v>
@@ -11070,7 +11070,7 @@
         <v>341</v>
       </c>
       <c r="J146" s="2">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>22</v>
@@ -11111,7 +11111,7 @@
         <v>348</v>
       </c>
       <c r="J147" s="5">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>22</v>
@@ -11152,7 +11152,7 @@
         <v>355</v>
       </c>
       <c r="J148" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>22</v>
@@ -11193,7 +11193,7 @@
         <v>362</v>
       </c>
       <c r="J149" s="5">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>22</v>
@@ -11234,7 +11234,7 @@
         <v>369</v>
       </c>
       <c r="J150" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>22</v>
@@ -11275,7 +11275,7 @@
         <v>376</v>
       </c>
       <c r="J151" s="5">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>22</v>
@@ -11316,7 +11316,7 @@
         <v>385</v>
       </c>
       <c r="J152" s="2">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>22</v>
@@ -11357,7 +11357,7 @@
         <v>392</v>
       </c>
       <c r="J153" s="5">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>22</v>
@@ -11398,7 +11398,7 @@
         <v>399</v>
       </c>
       <c r="J154" s="2">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>22</v>
@@ -11439,7 +11439,7 @@
         <v>406</v>
       </c>
       <c r="J155" s="5">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>22</v>
@@ -11480,7 +11480,7 @@
         <v>413</v>
       </c>
       <c r="J156" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>22</v>
@@ -11562,7 +11562,7 @@
         <v>427</v>
       </c>
       <c r="J158" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>22</v>
@@ -11603,7 +11603,7 @@
         <v>434</v>
       </c>
       <c r="J159" s="5">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>22</v>
@@ -11644,7 +11644,7 @@
         <v>441</v>
       </c>
       <c r="J160" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>22</v>
@@ -11685,7 +11685,7 @@
         <v>448</v>
       </c>
       <c r="J161" s="5">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>22</v>
@@ -11726,7 +11726,7 @@
         <v>457</v>
       </c>
       <c r="J162" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>22</v>
@@ -11767,7 +11767,7 @@
         <v>464</v>
       </c>
       <c r="J163" s="5">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>22</v>
@@ -11808,7 +11808,7 @@
         <v>471</v>
       </c>
       <c r="J164" s="2">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>22</v>
@@ -11849,7 +11849,7 @@
         <v>478</v>
       </c>
       <c r="J165" s="5">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>22</v>
@@ -11890,7 +11890,7 @@
         <v>485</v>
       </c>
       <c r="J166" s="2">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>22</v>
@@ -11931,7 +11931,7 @@
         <v>492</v>
       </c>
       <c r="J167" s="5">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>22</v>
@@ -11972,7 +11972,7 @@
         <v>499</v>
       </c>
       <c r="J168" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>22</v>
@@ -12013,7 +12013,7 @@
         <v>506</v>
       </c>
       <c r="J169" s="5">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>22</v>
@@ -12054,7 +12054,7 @@
         <v>513</v>
       </c>
       <c r="J170" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>22</v>
@@ -12095,7 +12095,7 @@
         <v>520</v>
       </c>
       <c r="J171" s="5">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>22</v>
@@ -12136,7 +12136,7 @@
         <v>529</v>
       </c>
       <c r="J172" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>22</v>
@@ -12177,7 +12177,7 @@
         <v>536</v>
       </c>
       <c r="J173" s="5">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="K173" s="4" t="s">
         <v>22</v>
@@ -12218,7 +12218,7 @@
         <v>543</v>
       </c>
       <c r="J174" s="2">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>22</v>
@@ -12259,7 +12259,7 @@
         <v>550</v>
       </c>
       <c r="J175" s="5">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>22</v>
@@ -12300,7 +12300,7 @@
         <v>557</v>
       </c>
       <c r="J176" s="2">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>22</v>
@@ -12341,7 +12341,7 @@
         <v>564</v>
       </c>
       <c r="J177" s="5">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>22</v>
@@ -12382,7 +12382,7 @@
         <v>571</v>
       </c>
       <c r="J178" s="2">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>22</v>
@@ -12423,7 +12423,7 @@
         <v>578</v>
       </c>
       <c r="J179" s="5">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>22</v>
@@ -12464,7 +12464,7 @@
         <v>585</v>
       </c>
       <c r="J180" s="2">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>22</v>
@@ -12505,7 +12505,7 @@
         <v>592</v>
       </c>
       <c r="J181" s="5">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>22</v>
@@ -12587,7 +12587,7 @@
         <v>608</v>
       </c>
       <c r="J183" s="5">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>22</v>
@@ -12628,7 +12628,7 @@
         <v>615</v>
       </c>
       <c r="J184" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="K184" s="4" t="s">
         <v>22</v>
@@ -12669,7 +12669,7 @@
         <v>622</v>
       </c>
       <c r="J185" s="5">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>22</v>
@@ -12710,7 +12710,7 @@
         <v>629</v>
       </c>
       <c r="J186" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>22</v>
@@ -12751,7 +12751,7 @@
         <v>636</v>
       </c>
       <c r="J187" s="5">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K187" s="4" t="s">
         <v>22</v>
@@ -12792,7 +12792,7 @@
         <v>643</v>
       </c>
       <c r="J188" s="2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>22</v>
@@ -12833,7 +12833,7 @@
         <v>650</v>
       </c>
       <c r="J189" s="5">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>22</v>
@@ -12874,7 +12874,7 @@
         <v>657</v>
       </c>
       <c r="J190" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>22</v>
@@ -12915,7 +12915,7 @@
         <v>664</v>
       </c>
       <c r="J191" s="5">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="K191" s="4" t="s">
         <v>22</v>
@@ -12956,7 +12956,7 @@
         <v>673</v>
       </c>
       <c r="J192" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K192" s="4" t="s">
         <v>22</v>
@@ -12997,7 +12997,7 @@
         <v>680</v>
       </c>
       <c r="J193" s="5">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K193" s="4" t="s">
         <v>22</v>
@@ -13038,7 +13038,7 @@
         <v>687</v>
       </c>
       <c r="J194" s="2">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="K194" s="4" t="s">
         <v>22</v>
@@ -13079,7 +13079,7 @@
         <v>694</v>
       </c>
       <c r="J195" s="5">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="K195" s="4" t="s">
         <v>22</v>
@@ -13120,7 +13120,7 @@
         <v>701</v>
       </c>
       <c r="J196" s="2">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K196" s="4" t="s">
         <v>22</v>
@@ -13161,7 +13161,7 @@
         <v>708</v>
       </c>
       <c r="J197" s="5">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K197" s="4" t="s">
         <v>22</v>
@@ -13202,7 +13202,7 @@
         <v>715</v>
       </c>
       <c r="J198" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K198" s="4" t="s">
         <v>22</v>
@@ -13243,7 +13243,7 @@
         <v>722</v>
       </c>
       <c r="J199" s="5">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K199" s="4" t="s">
         <v>22</v>
@@ -13284,7 +13284,7 @@
         <v>729</v>
       </c>
       <c r="J200" s="2">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="K200" s="4" t="s">
         <v>22</v>
@@ -13325,7 +13325,7 @@
         <v>736</v>
       </c>
       <c r="J201" s="5">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K201" s="4" t="s">
         <v>22</v>
@@ -13366,7 +13366,7 @@
         <v>21</v>
       </c>
       <c r="J202" s="2">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="K202" s="4" t="s">
         <v>22</v>
@@ -13407,7 +13407,7 @@
         <v>30</v>
       </c>
       <c r="J203" s="5">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K203" s="4" t="s">
         <v>22</v>
@@ -13448,7 +13448,7 @@
         <v>38</v>
       </c>
       <c r="J204" s="2">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="K204" s="4" t="s">
         <v>22</v>
@@ -13489,7 +13489,7 @@
         <v>45</v>
       </c>
       <c r="J205" s="5">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="K205" s="4" t="s">
         <v>22</v>
@@ -13530,7 +13530,7 @@
         <v>52</v>
       </c>
       <c r="J206" s="2">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="K206" s="4" t="s">
         <v>22</v>
@@ -13571,7 +13571,7 @@
         <v>60</v>
       </c>
       <c r="J207" s="5">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="K207" s="4" t="s">
         <v>22</v>
@@ -13612,7 +13612,7 @@
         <v>67</v>
       </c>
       <c r="J208" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K208" s="4" t="s">
         <v>22</v>
@@ -13653,7 +13653,7 @@
         <v>74</v>
       </c>
       <c r="J209" s="5">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="K209" s="4" t="s">
         <v>22</v>
@@ -13694,7 +13694,7 @@
         <v>81</v>
       </c>
       <c r="J210" s="2">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="K210" s="4" t="s">
         <v>22</v>
@@ -13735,7 +13735,7 @@
         <v>88</v>
       </c>
       <c r="J211" s="5">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="K211" s="4" t="s">
         <v>22</v>
@@ -13776,7 +13776,7 @@
         <v>97</v>
       </c>
       <c r="J212" s="2">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K212" s="4" t="s">
         <v>22</v>
@@ -13817,7 +13817,7 @@
         <v>104</v>
       </c>
       <c r="J213" s="5">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K213" s="4" t="s">
         <v>22</v>
@@ -13858,7 +13858,7 @@
         <v>111</v>
       </c>
       <c r="J214" s="2">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K214" s="4" t="s">
         <v>22</v>
@@ -13899,7 +13899,7 @@
         <v>118</v>
       </c>
       <c r="J215" s="5">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="K215" s="4" t="s">
         <v>22</v>
@@ -13940,7 +13940,7 @@
         <v>125</v>
       </c>
       <c r="J216" s="2">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K216" s="4" t="s">
         <v>22</v>
@@ -13981,7 +13981,7 @@
         <v>132</v>
       </c>
       <c r="J217" s="5">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="K217" s="4" t="s">
         <v>22</v>
@@ -14022,7 +14022,7 @@
         <v>139</v>
       </c>
       <c r="J218" s="2">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="K218" s="4" t="s">
         <v>22</v>
@@ -14063,7 +14063,7 @@
         <v>146</v>
       </c>
       <c r="J219" s="5">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="K219" s="4" t="s">
         <v>22</v>
@@ -14104,7 +14104,7 @@
         <v>153</v>
       </c>
       <c r="J220" s="2">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="K220" s="4" t="s">
         <v>22</v>
@@ -14145,7 +14145,7 @@
         <v>160</v>
       </c>
       <c r="J221" s="5">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K221" s="4" t="s">
         <v>22</v>
@@ -14227,7 +14227,7 @@
         <v>176</v>
       </c>
       <c r="J223" s="5">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K223" s="4" t="s">
         <v>22</v>
@@ -14268,7 +14268,7 @@
         <v>183</v>
       </c>
       <c r="J224" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>22</v>
@@ -14309,7 +14309,7 @@
         <v>190</v>
       </c>
       <c r="J225" s="5">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>22</v>
@@ -14350,7 +14350,7 @@
         <v>197</v>
       </c>
       <c r="J226" s="2">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="K226" s="4" t="s">
         <v>22</v>
@@ -14391,7 +14391,7 @@
         <v>204</v>
       </c>
       <c r="J227" s="5">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="K227" s="4" t="s">
         <v>22</v>
@@ -14432,7 +14432,7 @@
         <v>211</v>
       </c>
       <c r="J228" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K228" s="4" t="s">
         <v>22</v>
@@ -14473,7 +14473,7 @@
         <v>218</v>
       </c>
       <c r="J229" s="5">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="K229" s="4" t="s">
         <v>22</v>
@@ -14514,7 +14514,7 @@
         <v>225</v>
       </c>
       <c r="J230" s="2">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="K230" s="4" t="s">
         <v>22</v>
@@ -14555,7 +14555,7 @@
         <v>232</v>
       </c>
       <c r="J231" s="5">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="K231" s="4" t="s">
         <v>22</v>
@@ -14596,7 +14596,7 @@
         <v>241</v>
       </c>
       <c r="J232" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K232" s="4" t="s">
         <v>22</v>
@@ -14637,7 +14637,7 @@
         <v>248</v>
       </c>
       <c r="J233" s="5">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="K233" s="4" t="s">
         <v>22</v>
@@ -14678,7 +14678,7 @@
         <v>255</v>
       </c>
       <c r="J234" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K234" s="4" t="s">
         <v>22</v>
@@ -14719,7 +14719,7 @@
         <v>262</v>
       </c>
       <c r="J235" s="5">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K235" s="4" t="s">
         <v>22</v>
@@ -14760,7 +14760,7 @@
         <v>269</v>
       </c>
       <c r="J236" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K236" s="4" t="s">
         <v>22</v>
@@ -14801,7 +14801,7 @@
         <v>276</v>
       </c>
       <c r="J237" s="5">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K237" s="4" t="s">
         <v>22</v>
@@ -14842,7 +14842,7 @@
         <v>283</v>
       </c>
       <c r="J238" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="K238" s="4" t="s">
         <v>22</v>
@@ -14883,7 +14883,7 @@
         <v>290</v>
       </c>
       <c r="J239" s="5">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="K239" s="4" t="s">
         <v>22</v>
@@ -14924,7 +14924,7 @@
         <v>297</v>
       </c>
       <c r="J240" s="2">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K240" s="4" t="s">
         <v>22</v>
@@ -14965,7 +14965,7 @@
         <v>304</v>
       </c>
       <c r="J241" s="5">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="K241" s="4" t="s">
         <v>22</v>
@@ -15006,7 +15006,7 @@
         <v>313</v>
       </c>
       <c r="J242" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>22</v>
@@ -15047,7 +15047,7 @@
         <v>320</v>
       </c>
       <c r="J243" s="5">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>22</v>
@@ -15088,7 +15088,7 @@
         <v>327</v>
       </c>
       <c r="J244" s="2">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="K244" s="4" t="s">
         <v>22</v>
@@ -15129,7 +15129,7 @@
         <v>334</v>
       </c>
       <c r="J245" s="5">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="K245" s="4" t="s">
         <v>22</v>
@@ -15170,7 +15170,7 @@
         <v>341</v>
       </c>
       <c r="J246" s="2">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="K246" s="4" t="s">
         <v>22</v>
@@ -15211,7 +15211,7 @@
         <v>348</v>
       </c>
       <c r="J247" s="5">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K247" s="4" t="s">
         <v>22</v>
@@ -15252,7 +15252,7 @@
         <v>355</v>
       </c>
       <c r="J248" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="K248" s="4" t="s">
         <v>22</v>
@@ -15293,7 +15293,7 @@
         <v>362</v>
       </c>
       <c r="J249" s="5">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="K249" s="4" t="s">
         <v>22</v>
@@ -15334,7 +15334,7 @@
         <v>369</v>
       </c>
       <c r="J250" s="2">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>22</v>
@@ -15375,7 +15375,7 @@
         <v>376</v>
       </c>
       <c r="J251" s="5">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="K251" s="4" t="s">
         <v>22</v>
@@ -15416,7 +15416,7 @@
         <v>385</v>
       </c>
       <c r="J252" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K252" s="4" t="s">
         <v>22</v>
@@ -15457,7 +15457,7 @@
         <v>392</v>
       </c>
       <c r="J253" s="5">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="K253" s="4" t="s">
         <v>22</v>
@@ -15498,7 +15498,7 @@
         <v>399</v>
       </c>
       <c r="J254" s="2">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="K254" s="4" t="s">
         <v>22</v>
@@ -15539,7 +15539,7 @@
         <v>406</v>
       </c>
       <c r="J255" s="5">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="K255" s="4" t="s">
         <v>22</v>
@@ -15580,7 +15580,7 @@
         <v>413</v>
       </c>
       <c r="J256" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K256" s="4" t="s">
         <v>22</v>
@@ -15621,7 +15621,7 @@
         <v>420</v>
       </c>
       <c r="J257" s="5">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="K257" s="4" t="s">
         <v>22</v>
@@ -15662,7 +15662,7 @@
         <v>427</v>
       </c>
       <c r="J258" s="2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K258" s="4" t="s">
         <v>22</v>
@@ -15703,7 +15703,7 @@
         <v>434</v>
       </c>
       <c r="J259" s="5">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="K259" s="4" t="s">
         <v>22</v>
@@ -15744,7 +15744,7 @@
         <v>441</v>
       </c>
       <c r="J260" s="2">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="K260" s="4" t="s">
         <v>22</v>
@@ -15785,7 +15785,7 @@
         <v>448</v>
       </c>
       <c r="J261" s="5">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="K261" s="4" t="s">
         <v>22</v>
@@ -15826,7 +15826,7 @@
         <v>457</v>
       </c>
       <c r="J262" s="2">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="K262" s="4" t="s">
         <v>22</v>
@@ -15867,7 +15867,7 @@
         <v>464</v>
       </c>
       <c r="J263" s="5">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>22</v>
@@ -15908,7 +15908,7 @@
         <v>471</v>
       </c>
       <c r="J264" s="2">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="K264" s="4" t="s">
         <v>22</v>
@@ -15949,7 +15949,7 @@
         <v>478</v>
       </c>
       <c r="J265" s="5">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="K265" s="4" t="s">
         <v>22</v>
@@ -15990,7 +15990,7 @@
         <v>485</v>
       </c>
       <c r="J266" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K266" s="4" t="s">
         <v>22</v>
@@ -16031,7 +16031,7 @@
         <v>492</v>
       </c>
       <c r="J267" s="5">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K267" s="4" t="s">
         <v>22</v>
@@ -16072,7 +16072,7 @@
         <v>499</v>
       </c>
       <c r="J268" s="2">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="K268" s="4" t="s">
         <v>22</v>
@@ -16113,7 +16113,7 @@
         <v>506</v>
       </c>
       <c r="J269" s="5">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="K269" s="4" t="s">
         <v>22</v>
@@ -16154,7 +16154,7 @@
         <v>513</v>
       </c>
       <c r="J270" s="2">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="K270" s="4" t="s">
         <v>22</v>
@@ -16195,7 +16195,7 @@
         <v>520</v>
       </c>
       <c r="J271" s="5">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K271" s="4" t="s">
         <v>22</v>
@@ -16236,7 +16236,7 @@
         <v>529</v>
       </c>
       <c r="J272" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="K272" s="4" t="s">
         <v>22</v>
@@ -16277,7 +16277,7 @@
         <v>536</v>
       </c>
       <c r="J273" s="5">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K273" s="4" t="s">
         <v>22</v>
@@ -16318,7 +16318,7 @@
         <v>543</v>
       </c>
       <c r="J274" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K274" s="4" t="s">
         <v>22</v>
@@ -16359,7 +16359,7 @@
         <v>550</v>
       </c>
       <c r="J275" s="5">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="K275" s="4" t="s">
         <v>22</v>
@@ -16400,7 +16400,7 @@
         <v>557</v>
       </c>
       <c r="J276" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K276" s="4" t="s">
         <v>22</v>
@@ -16441,7 +16441,7 @@
         <v>564</v>
       </c>
       <c r="J277" s="5">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="K277" s="4" t="s">
         <v>22</v>
@@ -16482,7 +16482,7 @@
         <v>571</v>
       </c>
       <c r="J278" s="2">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="K278" s="4" t="s">
         <v>22</v>
@@ -16523,7 +16523,7 @@
         <v>578</v>
       </c>
       <c r="J279" s="5">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="K279" s="4" t="s">
         <v>22</v>
@@ -16564,7 +16564,7 @@
         <v>585</v>
       </c>
       <c r="J280" s="2">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="K280" s="4" t="s">
         <v>22</v>
@@ -16605,7 +16605,7 @@
         <v>592</v>
       </c>
       <c r="J281" s="5">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="K281" s="4" t="s">
         <v>22</v>
@@ -16646,7 +16646,7 @@
         <v>601</v>
       </c>
       <c r="J282" s="2">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K282" s="4" t="s">
         <v>22</v>
@@ -16687,7 +16687,7 @@
         <v>608</v>
       </c>
       <c r="J283" s="5">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="K283" s="4" t="s">
         <v>22</v>
@@ -16728,7 +16728,7 @@
         <v>615</v>
       </c>
       <c r="J284" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K284" s="4" t="s">
         <v>22</v>
@@ -16769,7 +16769,7 @@
         <v>622</v>
       </c>
       <c r="J285" s="5">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K285" s="4" t="s">
         <v>22</v>
@@ -16810,7 +16810,7 @@
         <v>629</v>
       </c>
       <c r="J286" s="2">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="K286" s="4" t="s">
         <v>22</v>
@@ -16851,7 +16851,7 @@
         <v>636</v>
       </c>
       <c r="J287" s="5">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="K287" s="4" t="s">
         <v>22</v>
@@ -16892,7 +16892,7 @@
         <v>643</v>
       </c>
       <c r="J288" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K288" s="4" t="s">
         <v>22</v>
@@ -16933,7 +16933,7 @@
         <v>650</v>
       </c>
       <c r="J289" s="5">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="K289" s="4" t="s">
         <v>22</v>
@@ -16974,7 +16974,7 @@
         <v>657</v>
       </c>
       <c r="J290" s="2">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="K290" s="4" t="s">
         <v>22</v>
@@ -17015,7 +17015,7 @@
         <v>664</v>
       </c>
       <c r="J291" s="5">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="K291" s="4" t="s">
         <v>22</v>
@@ -17056,7 +17056,7 @@
         <v>673</v>
       </c>
       <c r="J292" s="2">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="K292" s="4" t="s">
         <v>22</v>
@@ -17097,7 +17097,7 @@
         <v>680</v>
       </c>
       <c r="J293" s="5">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="K293" s="4" t="s">
         <v>22</v>
@@ -17138,7 +17138,7 @@
         <v>687</v>
       </c>
       <c r="J294" s="2">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="K294" s="4" t="s">
         <v>22</v>
@@ -17179,7 +17179,7 @@
         <v>694</v>
       </c>
       <c r="J295" s="5">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="K295" s="4" t="s">
         <v>22</v>
@@ -17220,7 +17220,7 @@
         <v>701</v>
       </c>
       <c r="J296" s="2">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="K296" s="4" t="s">
         <v>22</v>
@@ -17261,7 +17261,7 @@
         <v>708</v>
       </c>
       <c r="J297" s="5">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K297" s="4" t="s">
         <v>22</v>
@@ -17302,7 +17302,7 @@
         <v>715</v>
       </c>
       <c r="J298" s="2">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="K298" s="4" t="s">
         <v>22</v>
@@ -17343,7 +17343,7 @@
         <v>722</v>
       </c>
       <c r="J299" s="5">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K299" s="4" t="s">
         <v>22</v>
@@ -17384,7 +17384,7 @@
         <v>729</v>
       </c>
       <c r="J300" s="2">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="K300" s="4" t="s">
         <v>22</v>
@@ -17425,7 +17425,7 @@
         <v>736</v>
       </c>
       <c r="J301" s="5">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K301" s="4" t="s">
         <v>22</v>
